--- a/セリフ編集/キャラタイプ別/お嬢様×お気楽.xlsx
+++ b/セリフ編集/キャラタイプ別/お嬢様×お気楽.xlsx
@@ -262,7 +262,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H167"/>
+  <dimension ref="A1:H241"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="F77" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">引き分けですか。それも悪くありません。</t>
+          <t xml:space="preserve">決着つかずですか。それも悪くありません。</t>
         </is>
       </c>
     </row>
@@ -3232,7 +3232,7 @@
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -3242,12 +3242,12 @@
       </c>
       <c r="C93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[1]</t>
+          <t xml:space="preserve">A2_uncrowned.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E93" t="inlineStr" s="2">
@@ -3257,14 +3257,14 @@
       </c>
       <c r="F93" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくし、こちらに残りますわ!ここ、とっても楽しいんですもの!</t>
+          <t xml:space="preserve">ベルトは叶いませんでしたけど、楽しかったですわ</t>
         </is>
       </c>
     </row>
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -3274,29 +3274,29 @@
       </c>
       <c r="C94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">A3_heel.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F94" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございますわ。前向きに検討いたしますの</t>
+          <t xml:space="preserve">最後くらいは素直になっても、よろしいかしら。楽しかったですわ</t>
         </is>
       </c>
     </row>
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -3306,125 +3306,125 @@
       </c>
       <c r="C95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">start.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">A4_veteran.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F95" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">条件をお聞かせくださいまし。それ次第ですわ</t>
+          <t xml:space="preserve">まあ、長かったこと。…でも、あっという間でしたわね</t>
         </is>
       </c>
     </row>
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[1]</t>
+          <t xml:space="preserve">B1_young.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F96" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、向こうのお茶会のほうが、わたくしの性に合っておりますの。</t>
+          <t xml:space="preserve">え…嘘でしょう…まだこれからでしたのに…</t>
         </is>
       </c>
     </row>
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[1]</t>
+          <t xml:space="preserve">B2_prime.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F97" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、そんな昔のこと、もう忘れていますわよ。</t>
+          <t xml:space="preserve">まあ…困りましたわね。これからでしたのに…</t>
         </is>
       </c>
     </row>
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F07_LEADER_LINES.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F07_LEADER_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[1]</t>
+          <t xml:space="preserve">B3_older.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F98" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、気安いところで申し上げますけれど、待遇、もう少しどうにか。</t>
+          <t xml:space="preserve">まあ、十分やりましたわね。いい人生でしたこと</t>
         </is>
       </c>
     </row>
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3434,29 +3434,29 @@
       </c>
       <c r="C99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[1]</t>
+          <t xml:space="preserve">B4_champion_injury.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F99" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近絶好調ですわ！ もっと上に行けそうですの</t>
+          <t xml:space="preserve">あら…ベルトを持ったまま、おしまいですのね…</t>
         </is>
       </c>
     </row>
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3466,29 +3466,29 @@
       </c>
       <c r="C100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES</t>
         </is>
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F100" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、もうこれ以上は？ まあ、十分ですわ</t>
+          <t xml:space="preserve">わたくし、こちらに残りますわ!ここ、とっても楽しいんですもの!</t>
         </is>
       </c>
     </row>
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3498,29 +3498,29 @@
       </c>
       <c r="C101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">raise_accept.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F101" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来れるとは思いませんでしたわ！</t>
+          <t xml:space="preserve">まあ、うれしい！ さすが社長ですこと。今年も楽しくまいりましょうね。</t>
         </is>
       </c>
     </row>
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3530,29 +3530,29 @@
       </c>
       <c r="C102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F102" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">順調に成長してますわ♪</t>
+          <t xml:space="preserve">ふふ、まあ良いことにいたしましょう。いただけるだけ幸運ですもの。</t>
         </is>
       </c>
     </row>
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3562,29 +3562,29 @@
       </c>
       <c r="C103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F103" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらまあ…とんでもないところまで来てしまいましたわ</t>
+          <t xml:space="preserve">あらら、だめですのね。まあ仕方ありません。……少し、しょげてしまいます。</t>
         </is>
       </c>
     </row>
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3594,29 +3594,29 @@
       </c>
       <c r="C104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_growth.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">raise_open.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F104" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンの方が増えて嬉しいですわ！</t>
+          <t xml:space="preserve">ありがとうございますわ。前向きに検討いたしますの</t>
         </is>
       </c>
     </row>
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3626,29 +3626,29 @@
       </c>
       <c r="C105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">raise_refuse.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F105" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、こんなに！ もっともっと楽しんでまいりましょう！</t>
+          <t xml:space="preserve">ふふ、やはりだめですのね。まあ仕方ありません。でも、いつか上げてくださいませ。約束ですわよ。</t>
         </is>
       </c>
     </row>
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3658,29 +3658,29 @@
       </c>
       <c r="C106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[1]</t>
+          <t xml:space="preserve">transfer_listen.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F106" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">少しやる気が出ませんの…でも頑張りますわ</t>
+          <t xml:space="preserve">聞いてくださるの？ そうねえ……{record}なんだか、代わり映えしなくて。新しいことがしてみたいの。</t>
         </is>
       </c>
     </row>
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3690,29 +3690,29 @@
       </c>
       <c r="C107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[1]</t>
+          <t xml:space="preserve">transfer_open.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F107" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やる気が戻ってまいりましたわ！ もう大丈夫ですの</t>
+          <t xml:space="preserve">社長、あのね。{tenure}いろいろ考えたのだけれど……環境を変えてみようかしら、と。</t>
         </is>
       </c>
     </row>
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3722,29 +3722,29 @@
       </c>
       <c r="C108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[1]</t>
+          <t xml:space="preserve">transfer_open.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F108" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">調子が戻ってまいりましたわ！ もう大丈夫ですの</t>
+          <t xml:space="preserve">いやはや社長。言いにくいのだけれど。{tenure}少し外の風に当たってみたくなって。</t>
         </is>
       </c>
     </row>
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3754,29 +3754,29 @@
       </c>
       <c r="C109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">transfer_release.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F109" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近少し不調ですの…でもすぐ立て直しますわ</t>
+          <t xml:space="preserve">ふふ、まあそうなりますわよね。{tenure_farewell}{rivalry}どうか、お元気で。</t>
         </is>
       </c>
     </row>
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3786,29 +3786,29 @@
       </c>
       <c r="C110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">transfer_retain_fail.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F110" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の試合でしたわ！ お相手にも感謝ですの</t>
+          <t xml:space="preserve">ごめんなさい社長……。お金の話ではないの。もう、心が決まってしまったから。</t>
         </is>
       </c>
     </row>
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3818,29 +3818,29 @@
       </c>
       <c r="C111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">transfer_retain_success.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F111" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一年間お守りいたしましたわ。来年もこの座を守りますの</t>
+          <t xml:space="preserve">あら、そこまでしてくださるの？ ……では、もう少しだけ居させていただこうかしら。</t>
         </is>
       </c>
     </row>
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3850,103 +3850,103 @@
       </c>
       <c r="C112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">start.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F112" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">殿堂入りですの…！ 夢のようですわ…</t>
+          <t xml:space="preserve">条件をお聞かせくださいまし。それ次第ですわ</t>
         </is>
       </c>
     </row>
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">FACTION_F04_TARGET_LINES.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">FACTION_F04_TARGET_LINES</t>
         </is>
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F113" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVPですの！ 光栄ですわ。来年も精進いたしますの</t>
+          <t xml:space="preserve">あら、向こうのお茶会のほうが、わたくしの性に合っておりますの。</t>
         </is>
       </c>
     </row>
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES</t>
         </is>
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ…！ 新人王ですの…！ 光栄ですわ</t>
+          <t xml:space="preserve">あら、そんな昔のこと、もう忘れていますわよ。</t>
         </is>
       </c>
     </row>
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">FACTION_F07_LEADER_LINES.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">FACTION_F07_LEADER_LINES</t>
         </is>
       </c>
       <c r="D115" t="inlineStr" s="12">
@@ -3956,19 +3956,19 @@
       </c>
       <c r="E115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、ドームですのね。なんだか楽しそうですわ</t>
+          <t xml:space="preserve">社長、気安いところで申し上げますけれど、待遇、もう少しどうにか。</t>
         </is>
       </c>
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -3978,29 +3978,29 @@
       </c>
       <c r="C116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[2]</t>
+          <t xml:space="preserve">easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ気楽にいきますわよ、ほほほ</t>
+          <t xml:space="preserve">最近絶好調ですわ！ もっと上に行けそうですの</t>
         </is>
       </c>
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.easygoing.ojousama[3]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4010,29 +4010,29 @@
       </c>
       <c r="C117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[3]</t>
+          <t xml:space="preserve">cap_reached.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こういう大きな会場、わたくし嫌いじゃありませんの</t>
+          <t xml:space="preserve">あら、もうこれ以上は？ まあ、十分ですわ</t>
         </is>
       </c>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4042,29 +4042,29 @@
       </c>
       <c r="C118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[1]</t>
+          <t xml:space="preserve">ovr_elite.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ、満員ですのね! 嬉しゅうございますわ</t>
+          <t xml:space="preserve">ここまで来れるとは思いませんでしたわ！</t>
         </is>
       </c>
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4074,29 +4074,29 @@
       </c>
       <c r="C119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[2]</t>
+          <t xml:space="preserve">ovr_growth.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなに楽しい日は、なかなかありませんの</t>
+          <t xml:space="preserve">順調に成長してますわ♪</t>
         </is>
       </c>
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.easygoing.ojousama[3]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4106,29 +4106,29 @@
       </c>
       <c r="C120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[3]</t>
+          <t xml:space="preserve">ovr_legend.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ほほほ、またやりたくなりますわ</t>
+          <t xml:space="preserve">あらまあ…とんでもないところまで来てしまいましたわ</t>
         </is>
       </c>
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4138,29 +4138,29 @@
       </c>
       <c r="C121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.accept.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">pop_growth.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F121" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、成功いたしましたの!わたくし、嬉しくて仕方ありませんわ!</t>
+          <t xml:space="preserve">ファンの方が増えて嬉しいですわ！</t>
         </is>
       </c>
     </row>
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4170,29 +4170,29 @@
       </c>
       <c r="C122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[1]</t>
+          <t xml:space="preserve">pop_star.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F122" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、よろしくお願いしますわぁ</t>
+          <t xml:space="preserve">まあ、こんなに！ もっともっと楽しんでまいりましょう！</t>
         </is>
       </c>
     </row>
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4202,29 +4202,29 @@
       </c>
       <c r="C123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[2]</t>
+          <t xml:space="preserve">easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F123" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お仲間入りですわね。よろしくですの</t>
+          <t xml:space="preserve">少しやる気が出ませんの…でも頑張りますわ</t>
         </is>
       </c>
     </row>
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="C124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D124" t="inlineStr" s="12">
@@ -4244,19 +4244,19 @@
       </c>
       <c r="E124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F124" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらあら…少し休みますわね</t>
+          <t xml:space="preserve">やる気が戻ってまいりましたわ！ もう大丈夫ですの</t>
         </is>
       </c>
     </row>
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4266,29 +4266,29 @@
       </c>
       <c r="C125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F125" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、よろしくお願いしますわぁ</t>
+          <t xml:space="preserve">調子が戻ってまいりましたわ！ もう大丈夫ですの</t>
         </is>
       </c>
     </row>
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4298,29 +4298,29 @@
       </c>
       <c r="C126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">defeat.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F126" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お仲間入りですわね。よろしくですの</t>
+          <t xml:space="preserve">最近少し不調ですの…でもすぐ立て直しますわ</t>
         </is>
       </c>
     </row>
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -4330,29 +4330,29 @@
       </c>
       <c r="C127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">bestMatch.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F127" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらあら…少し休みますわね</t>
+          <t xml:space="preserve">最高の試合でしたわ！ お相手にも感謝ですの</t>
         </is>
       </c>
     </row>
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4362,29 +4362,29 @@
       </c>
       <c r="C128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">champion.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F128" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、こういうこともありますわね。ごきげんよう</t>
+          <t xml:space="preserve">一年間お守りいたしましたわ。来年もこの座を守りますの</t>
         </is>
       </c>
     </row>
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4394,29 +4394,29 @@
       </c>
       <c r="C129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[1]</t>
+          <t xml:space="preserve">hallOfFame.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F129" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、こういうこともありますわね。ごきげんよう</t>
+          <t xml:space="preserve">殿堂入りですの…！ 夢のようですわ…</t>
         </is>
       </c>
     </row>
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4426,29 +4426,29 @@
       </c>
       <c r="C130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">mvp.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しくお過ごしできますの〜</t>
+          <t xml:space="preserve">MVPですの！ 光栄ですわ。来年も精進いたしますの</t>
         </is>
       </c>
     </row>
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4458,29 +4458,29 @@
       </c>
       <c r="C131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[1]</t>
+          <t xml:space="preserve">rookie.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">連勝が止まりましたわ…でもまた頑張りますの</t>
+          <t xml:space="preserve">まあ…！ 新人王ですの…！ 光栄ですわ</t>
         </is>
       </c>
     </row>
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4490,29 +4490,29 @@
       </c>
       <c r="C132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">傷だらけですけれど、最後まで来てしまいましたわ。ふふ、やるしかありませんわね</t>
+          <t xml:space="preserve">あら、ドームですのね。なんだか楽しそうですわ</t>
         </is>
       </c>
     </row>
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4522,29 +4522,29 @@
       </c>
       <c r="C133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">さすがに身体が重いですの。でも、締めくくりは楽しませていただきますわ</t>
+          <t xml:space="preserve">まぁ気楽にいきますわよ、ほほほ</t>
         </is>
       </c>
     </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.easygoing.ojousama[3]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4554,29 +4554,29 @@
       </c>
       <c r="C134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">easygoing.ojousama[3]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、お相手はどなた? 次から次へと、賑やかですこと</t>
+          <t xml:space="preserve">こういう大きな会場、わたくし嫌いじゃありませんの</t>
         </is>
       </c>
     </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4586,29 +4586,29 @@
       </c>
       <c r="C135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">賑やかな一日になりそうですわね。…面白いですわ</t>
+          <t xml:space="preserve">まぁ、満員ですのね! 嬉しゅうございますわ</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4618,29 +4618,29 @@
       </c>
       <c r="C136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、お見送りしましたわ。…ふぅ、まだ立っていますのよ。次はどなた?</t>
+          <t xml:space="preserve">こんなに楽しい日は、なかなかありませんの</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.easygoing.ojousama[3]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4650,29 +4650,29 @@
       </c>
       <c r="C137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">easygoing.ojousama[3]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、まだ終わりませんの? いいですわ、次の方、いらして</t>
+          <t xml:space="preserve">ほほほ、またやりたくなりますわ</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4682,29 +4682,29 @@
       </c>
       <c r="C138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">E1.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">素敵な三人でしたわ。この勝利は、お二人と分かち合いたいですの</t>
+          <t xml:space="preserve">ファンの皆さまに、もっと近くで見ていただきたいんです</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4714,29 +4714,29 @@
       </c>
       <c r="C139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">E1.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お二人がいてくださったから、安心して戦えましたわ。ふふ</t>
+          <t xml:space="preserve">テレビ…！わたくし、出てみたいです</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4746,29 +4746,29 @@
       </c>
       <c r="C140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
         </is>
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">E1.accept.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お賞はありがたいですわ。でも……お一人で笑うのは、趣味じゃありませんの</t>
+          <t xml:space="preserve">まあ、成功いたしましたの!わたくし、嬉しくて仕方ありませんわ!</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4778,29 +4778,29 @@
       </c>
       <c r="C141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次はお三人で勝って、優雅に乾杯したいですわね</t>
+          <t xml:space="preserve">うふふ、ご一緒に楽しくやりましょうよ</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4810,29 +4810,29 @@
       </c>
       <c r="C142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次から次へと来るのですもの。退屈しませんでしたわ。身体は少し重いですけれど</t>
+          <t xml:space="preserve">退屈なプロレスはしないと約束いたしますわ</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4842,29 +4842,29 @@
       </c>
       <c r="C143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人お相手したのかしら。まあ、全員お見送りしましたし、よろしいですわね</t>
+          <t xml:space="preserve">ふふ、よろしくお願いしますわぁ</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4874,29 +4874,29 @@
       </c>
       <c r="C144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、優勝ですの！ 最高ですわ〜！</t>
+          <t xml:space="preserve">お仲間入りですわね。よろしくですの</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4906,29 +4906,29 @@
       </c>
       <c r="C145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やりましたわ〜！ ご褒美が楽しみですわね</t>
+          <t xml:space="preserve">ごきげんよう。新天地ですわ、暴れさせていただきますの</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4938,29 +4938,29 @@
       </c>
       <c r="C146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やりましたわ。この調子で行きますわよ</t>
+          <t xml:space="preserve">ここなら好きにやれそうですわね。楽しみですの</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -4970,29 +4970,29 @@
       </c>
       <c r="C147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだまだ楽しめそうですわね</t>
+          <t xml:space="preserve">まあ、今日から仲間ですわね。よろしくお願いしますの</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5002,29 +5002,29 @@
       </c>
       <c r="C148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、決勝まで来ちゃいましたわ。楽しみですわね</t>
+          <t xml:space="preserve">皆様、楽しくやりましょうね</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5034,29 +5034,29 @@
       </c>
       <c r="C149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最後の一戦！ 思いっきりやりますわよ</t>
+          <t xml:space="preserve">あらあら…少し休みますわね</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5066,29 +5066,29 @@
       </c>
       <c r="C150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">draftInterest.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">さあ、楽しい時間の始まりですわ</t>
+          <t xml:space="preserve">うふふ、ご一緒に楽しくやりましょうよ</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5098,29 +5098,29 @@
       </c>
       <c r="C151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">draftInterest.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">気楽に参りましょう。でも負けませんわよ</t>
+          <t xml:space="preserve">退屈なプロレスはしないと約束いたしますわ</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5130,29 +5130,29 @@
       </c>
       <c r="C152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">draftJoin.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、わたくしも呼ばれましたの？ 面白そうですわね</t>
+          <t xml:space="preserve">ふふ、よろしくお願いしますわぁ</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5162,29 +5162,29 @@
       </c>
       <c r="C153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">draftJoin.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしが選ばれないわけがありませんわよね</t>
+          <t xml:space="preserve">お仲間入りですわね。よろしくですの</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5194,29 +5194,29 @@
       </c>
       <c r="C154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[1]</t>
+          <t xml:space="preserve">faGreeting.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力で参りますわ！ よろしくお願いいたしますの</t>
+          <t xml:space="preserve">巡り巡って、良い場所にご縁がありましたこと</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5226,29 +5226,29 @@
       </c>
       <c r="C155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[1]</t>
+          <t xml:space="preserve">faSigning.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、勝っちゃいましたわ!最高の舞台で、最高の気分ですの!</t>
+          <t xml:space="preserve">ごきげんよう。新天地ですわ、暴れさせていただきますの</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5258,29 +5258,29 @@
       </c>
       <c r="C156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[1]</t>
+          <t xml:space="preserve">faSigning.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら〜、面白そうな団体ですわね。遊ばせていただきますわ</t>
+          <t xml:space="preserve">ここなら好きにやれそうですわね。楽しみですの</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5290,29 +5290,29 @@
       </c>
       <c r="C157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[2]</t>
+          <t xml:space="preserve">faWelcome.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしたちと勝負しません？ きっと楽しいですわよ</t>
+          <t xml:space="preserve">まあ、今日から仲間ですわね。よろしくお願いしますの</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5322,29 +5322,29 @@
       </c>
       <c r="C158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[1]</t>
+          <t xml:space="preserve">faWelcome.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら〜、お断りですの？ もったいないですわ</t>
+          <t xml:space="preserve">皆様、楽しくやりましょうね</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5354,29 +5354,29 @@
       </c>
       <c r="C159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[2]</t>
+          <t xml:space="preserve">injury.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、いいですわ。またの機会にいたしましょう</t>
+          <t xml:space="preserve">あらあら…少し休みますわね</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5386,29 +5386,29 @@
       </c>
       <c r="C160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">release.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらあら、負けてしまいましたわ。でもくよくよしませんわ</t>
+          <t xml:space="preserve">ふふ、こういうこともありますわね。ごきげんよう</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5418,29 +5418,29 @@
       </c>
       <c r="C161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">rentalGreeting.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次はもっと上手くやりますわよ〜</t>
+          <t xml:space="preserve">お邪魔いたしますわ。短い間ですけれど、暴れさせていただきますの</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5450,29 +5450,29 @@
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">rentalGreeting.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やりましたわ〜！ 勝利ですわ！</t>
+          <t xml:space="preserve">一時のご縁ですもの、思い切りやらせていただきますわ</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5482,29 +5482,29 @@
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">scoutGreeting.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しい対抗戦でしたわ。またぜひ</t>
+          <t xml:space="preserve">うふふ♪見出されるって、とても気分がよいことですね</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5514,29 +5514,29 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、勝ってしまいましたわ～。うちの団体、なかなかやりますでしょ？</t>
+          <t xml:space="preserve">今日は負けてしまいましたけれど…次はもっとよい試合をしますわ</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5546,29 +5546,29 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[2]</t>
+          <t xml:space="preserve">titleChallengeLoss.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらあら、勝っちゃいましたわね〜</t>
+          <t xml:space="preserve">悔しいですけれど、俯いていては応援してくださる方に失礼ですもの</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.easygoing.ojousama[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5578,59 +5578,2427 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[3]</t>
+          <t xml:space="preserve">titleDefense.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しかったですわ〜。またやりましょうね</t>
+          <t xml:space="preserve">チャンピオンはわたくしですの。また守り切りましたわ</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">titleDefense.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">よい試合でしたわ。またいつでも挑んでらして</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="40" customHeight="1">
+      <c r="A168" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">titleLoss.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">負けてしまいましたわ…でも応援してくださる方がいる限り、立ち上がりますの</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="40" customHeight="1">
+      <c r="A169" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">titleLoss.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ベルトのないわたくしなんて想像もできませんでしたわ。でも、わたくしはわたくしですもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="40" customHeight="1">
+      <c r="A170" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">titleWin.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">新チャンピオン誕生ですわ。ここからもっと盛り上げますの</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="40" customHeight="1">
+      <c r="A171" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">titleWin.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ベルト、獲ってしまいましたわ。最高の気分ですの</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="40" customHeight="1">
+      <c r="A172" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ふふ、こういうこともありますわね。ごきげんよう</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="40" customHeight="1">
+      <c r="A173" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">お邪魔いたしますわ。短い間ですけれど、暴れさせていただきますの</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="40" customHeight="1">
+      <c r="A174" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">一時のご縁ですもの、思い切りやらせていただきますわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="40" customHeight="1">
+      <c r="A175" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">今日は負けてしまいましたけれど…次はもっとよい試合をしますわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="40" customHeight="1">
+      <c r="A176" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">悔しいですけれど、俯いていては応援してくださる方に失礼ですもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="40" customHeight="1">
+      <c r="A177" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">チャンピオンはわたくしですの。また守り切りましたわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="40" customHeight="1">
+      <c r="A178" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">よい試合でしたわ。またいつでも挑んでらして</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="40" customHeight="1">
+      <c r="A179" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">負けてしまいましたわ…でも応援してくださる方がいる限り、立ち上がりますの</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="40" customHeight="1">
+      <c r="A180" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ベルトのないわたくしなんて想像もできませんでしたわ。でも、わたくしはわたくしですもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="40" customHeight="1">
+      <c r="A181" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">新チャンピオン誕生ですわ。ここからもっと盛り上げますの</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="40" customHeight="1">
+      <c r="A182" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ベルト、獲ってしまいましたわ。最高の気分ですの</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="40" customHeight="1">
+      <c r="A183" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_39_down.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">う〜ん…少々、合いませんかしら…</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="40" customHeight="1">
+      <c r="A184" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_59_down.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あら、近ごろ少し素っ気ないような</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="40" customHeight="1">
+      <c r="A185" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_59_down.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">はて…空気が微かに変わりましたかしら</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="40" customHeight="1">
+      <c r="A186" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_60_up.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">楽しくお過ごしできますの〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="40" customHeight="1">
+      <c r="A187" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_80_up.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">最高の相方。ずっとこのままでいたいものです</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="40" customHeight="1">
+      <c r="A188" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_80_up.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">一緒にいると、何もかも上手く回る気がして</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="40" customHeight="1">
+      <c r="A189" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_29_down.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">熱い間柄も一区切り。少し寂しいものです</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="40" customHeight="1">
+      <c r="A190" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_29_down.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まぁ、因縁とて永遠ではありませんもの〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="40" customHeight="1">
+      <c r="A191" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_30_up.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">良い勝負になりそうです〜。少し燃えてきました</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="40" customHeight="1">
+      <c r="A192" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_30_up.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">うふふ、負けたくありませんね</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="40" customHeight="1">
+      <c r="A193" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_50_up.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">本気でやり合いたい相手など、そういません</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="40" customHeight="1">
+      <c r="A194" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_50_up.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">うふふ、思い浮かべるだけで力が入ります</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="40" customHeight="1">
+      <c r="A195" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_70_up.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">この試合が一番楽しい。ずっとこのままであればよいのに</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="40" customHeight="1">
+      <c r="A196" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_70_up.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">運命の好敵手…そう呼びたくなります</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="40" customHeight="1">
+      <c r="A197" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_above_75.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ここは素晴らしい〜。皆さんとやるのが楽しくて</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="40" customHeight="1">
+      <c r="A198" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_above_75.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">この団体、とても居心地がよいのです〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="40" customHeight="1">
+      <c r="A199" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_below_20.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">さすがにこれは…笑えません</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="40" customHeight="1">
+      <c r="A200" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_below_20.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">うふふ…と笑っている場合ではありませんね、これは</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="40" customHeight="1">
+      <c r="A201" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_below_35.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">う〜ん…近ごろ少し胸がすっきりしません…</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="40" customHeight="1">
+      <c r="A202" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_below_35.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まぁ大丈夫…ですよね？ 少し不安ですけれど</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="40" customHeight="1">
+      <c r="A203" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">連勝が止まりましたわ…でもまた頑張りますの</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="40" customHeight="1">
+      <c r="A204" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">傷だらけですけれど、最後まで来てしまいましたわ。ふふ、やるしかありませんわね</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="40" customHeight="1">
+      <c r="A205" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">さすがに身体が重いですの。でも、締めくくりは楽しませていただきますわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="40" customHeight="1">
+      <c r="A206" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あら、お相手はどなた? 次から次へと、賑やかですこと</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="40" customHeight="1">
+      <c r="A207" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">賑やかな一日になりそうですわね。…面白いですわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="40" customHeight="1">
+      <c r="A208" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">survivor.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">一人、お見送りしましたわ。…ふぅ、まだ立っていますのよ。次はどなた?</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="40" customHeight="1">
+      <c r="A209" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">survivor.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あら、まだ終わりませんの? いいですわ、次の方、いらして</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="40" customHeight="1">
+      <c r="A210" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">素敵な三人でしたわ。この勝利は、お二人と分かち合いたいですの</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="40" customHeight="1">
+      <c r="A211" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">お二人がいてくださったから、安心して戦えましたわ。ふふ</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="40" customHeight="1">
+      <c r="A212" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">defiant.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">お賞はありがたいですわ。でも……お一人で笑うのは、趣味じゃありませんの</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="40" customHeight="1">
+      <c r="A213" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">defiant.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">次はお三人で勝って、優雅に乾杯したいですわね</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" ht="40" customHeight="1">
+      <c r="A214" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">次から次へと来るのですもの。退屈しませんでしたわ。身体は少し重いですけれど</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="40" customHeight="1">
+      <c r="A215" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">何人お相手したのかしら。まあ、全員お見送りしましたし、よろしいですわね</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="40" customHeight="1">
+      <c r="A216" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まあ、優勝ですの！ 最高ですわ〜！</t>
+        </is>
+      </c>
+    </row>
+    <row r="217" ht="40" customHeight="1">
+      <c r="A217" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">やりましたわ〜！ ご褒美が楽しみですわね</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="40" customHeight="1">
+      <c r="A218" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postMatchWin.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">やりましたわ。この調子で行きますわよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="40" customHeight="1">
+      <c r="A219" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postMatchWin.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まだまだ楽しめそうですわね</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="40" customHeight="1">
+      <c r="A220" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あら、決勝まで来ちゃいましたわ。楽しみですわね</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="40" customHeight="1">
+      <c r="A221" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">最後の一戦！ 思いっきりやりますわよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="40" customHeight="1">
+      <c r="A222" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">さあ、楽しい時間の始まりですわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="40" customHeight="1">
+      <c r="A223" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">気楽に参りましょう。でも負けませんわよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" ht="40" customHeight="1">
+      <c r="A224" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">summon.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あら、わたくしも呼ばれましたの？ 面白そうですわね</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" ht="40" customHeight="1">
+      <c r="A225" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">summon.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">わたくしが選ばれないわけがありませんわよね</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="40" customHeight="1">
+      <c r="A226" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">全力で参りますわ！ よろしくお願いいたしますの</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="40" customHeight="1">
+      <c r="A227" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まあ、勝っちゃいましたわ!最高の舞台で、最高の気分ですの!</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" ht="40" customHeight="1">
+      <c r="A228" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あら〜、面白そうな団体ですわね。遊ばせていただきますわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="40" customHeight="1">
+      <c r="A229" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">わたくしたちと勝負しません？ きっと楽しいですわよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="230" ht="40" customHeight="1">
+      <c r="A230" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あら〜、お断りですの？ もったいないですわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" ht="40" customHeight="1">
+      <c r="A231" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ま、いいですわ。またの機会にいたしましょう</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="40" customHeight="1">
+      <c r="A232" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_lose.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あらあら、負けてしまいましたわ。でもくよくよしませんわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="233" ht="40" customHeight="1">
+      <c r="A233" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_lose.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">次はもっと上手くやりますわよ〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" ht="40" customHeight="1">
+      <c r="A234" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">やりましたわ〜！ 勝利ですわ！</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" ht="40" customHeight="1">
+      <c r="A235" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">楽しい対抗戦でしたわ。またぜひ</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="40" customHeight="1">
+      <c r="A236" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あら、勝ってしまいましたわ～。うちの団体、なかなかやりますでしょ？</t>
+        </is>
+      </c>
+    </row>
+    <row r="237" ht="40" customHeight="1">
+      <c r="A237" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あらあら、勝っちゃいましたわね〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="40" customHeight="1">
+      <c r="A238" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.easygoing.ojousama[3]</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.ojousama[3]</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">楽しかったですわ〜。またやりましょうね</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" ht="40" customHeight="1">
+      <c r="A239" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">ENDING_LINES.fighter.easygoing.ojousama[1]</t>
         </is>
       </c>
-      <c r="B167" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr" s="2">
+      <c r="B239" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr" s="12">
+      <c r="D239" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fighter.easygoing.ojousama[1]</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr" s="2">
+      <c r="E239" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
-      <c r="F167" t="inlineStr" s="3">
+      <c r="F239" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">最後まで楽しゅうございましたわ。ありがとうございます</t>
         </is>
       </c>
     </row>
+    <row r="240" ht="40" customHeight="1">
+      <c r="A240" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">巡り巡って、良い場所にご縁がありましたこと</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" ht="40" customHeight="1">
+      <c r="A241" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.ojousama[1]</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">うふふ♪見出されるって、とても気分がよいことですね</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H167"/>
+  <autoFilter ref="A1:H241"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/お嬢様×お気楽.xlsx
+++ b/セリフ編集/キャラタイプ別/お嬢様×お気楽.xlsx
@@ -262,7 +262,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H241"/>
+  <dimension ref="A1:H280"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -320,7 +320,7 @@
     <row r="2" ht="40" customHeight="1">
       <c r="A2" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="2">
@@ -335,7 +335,7 @@
       </c>
       <c r="D2" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">atk.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr" s="2">
@@ -352,7 +352,7 @@
     <row r="3" ht="40" customHeight="1">
       <c r="A3" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
@@ -367,7 +367,7 @@
       </c>
       <c r="D3" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">atk.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr" s="2">
@@ -384,7 +384,7 @@
     <row r="4" ht="40" customHeight="1">
       <c r="A4" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.easygoing.ojousama[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.ojousama.easygoing[3]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
@@ -399,7 +399,7 @@
       </c>
       <c r="D4" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.easygoing.ojousama[3]</t>
+          <t xml:space="preserve">atk.ojousama.easygoing[3]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr" s="2">
@@ -416,7 +416,7 @@
     <row r="5" ht="40" customHeight="1">
       <c r="A5" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.easygoing.ojousama[4]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.ojousama.easygoing[4]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
@@ -431,7 +431,7 @@
       </c>
       <c r="D5" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.easygoing.ojousama[4]</t>
+          <t xml:space="preserve">atk.ojousama.easygoing[4]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr" s="2">
@@ -448,7 +448,7 @@
     <row r="6" ht="40" customHeight="1">
       <c r="A6" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
@@ -463,7 +463,7 @@
       </c>
       <c r="D6" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">bigmove.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr" s="2">
@@ -480,7 +480,7 @@
     <row r="7" ht="40" customHeight="1">
       <c r="A7" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
@@ -495,7 +495,7 @@
       </c>
       <c r="D7" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">bigmove.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr" s="2">
@@ -512,7 +512,7 @@
     <row r="8" ht="40" customHeight="1">
       <c r="A8" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.easygoing.ojousama[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.ojousama.easygoing[3]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
@@ -527,7 +527,7 @@
       </c>
       <c r="D8" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.easygoing.ojousama[3]</t>
+          <t xml:space="preserve">bigmove.ojousama.easygoing[3]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr" s="2">
@@ -544,7 +544,7 @@
     <row r="9" ht="40" customHeight="1">
       <c r="A9" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
@@ -559,7 +559,7 @@
       </c>
       <c r="D9" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">climax.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr" s="2">
@@ -576,7 +576,7 @@
     <row r="10" ht="40" customHeight="1">
       <c r="A10" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
@@ -591,7 +591,7 @@
       </c>
       <c r="D10" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">climax.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr" s="2">
@@ -608,7 +608,7 @@
     <row r="11" ht="40" customHeight="1">
       <c r="A11" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
@@ -623,7 +623,7 @@
       </c>
       <c r="D11" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr" s="2">
@@ -640,7 +640,7 @@
     <row r="12" ht="40" customHeight="1">
       <c r="A12" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
@@ -655,7 +655,7 @@
       </c>
       <c r="D12" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr" s="2">
@@ -672,7 +672,7 @@
     <row r="13" ht="40" customHeight="1">
       <c r="A13" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.easygoing.ojousama[3]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.ojousama.easygoing[3]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
@@ -687,7 +687,7 @@
       </c>
       <c r="D13" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[3]</t>
+          <t xml:space="preserve">ojousama.easygoing[3]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr" s="2">
@@ -704,7 +704,7 @@
     <row r="14" ht="40" customHeight="1">
       <c r="A14" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
@@ -719,7 +719,7 @@
       </c>
       <c r="D14" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">badWinner.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">badWinner.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr" s="2">
@@ -736,7 +736,7 @@
     <row r="15" ht="40" customHeight="1">
       <c r="A15" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
@@ -751,7 +751,7 @@
       </c>
       <c r="D15" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">goodWinner.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">goodWinner.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr" s="2">
@@ -768,7 +768,7 @@
     <row r="16" ht="40" customHeight="1">
       <c r="A16" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FIRST_MEET_LINES.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">FIRST_MEET_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
@@ -783,7 +783,7 @@
       </c>
       <c r="D16" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr" s="2">
@@ -800,7 +800,7 @@
     <row r="17" ht="40" customHeight="1">
       <c r="A17" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.loser.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
@@ -815,7 +815,7 @@
       </c>
       <c r="D17" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">loser.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr" s="2">
@@ -832,7 +832,7 @@
     <row r="18" ht="40" customHeight="1">
       <c r="A18" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">POST_MATCH_FLAVOR_LINES.winner.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
@@ -847,7 +847,7 @@
       </c>
       <c r="D18" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">winner.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr" s="2">
@@ -864,7 +864,7 @@
     <row r="19" ht="40" customHeight="1">
       <c r="A19" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
@@ -879,7 +879,7 @@
       </c>
       <c r="D19" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">competition_won.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr" s="2">
@@ -896,7 +896,7 @@
     <row r="20" ht="40" customHeight="1">
       <c r="A20" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
@@ -911,7 +911,7 @@
       </c>
       <c r="D20" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">direct.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr" s="2">
@@ -928,7 +928,7 @@
     <row r="21" ht="40" customHeight="1">
       <c r="A21" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
@@ -943,7 +943,7 @@
       </c>
       <c r="D21" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fa_signing.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">fa_signing.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr" s="2">
@@ -960,7 +960,7 @@
     <row r="22" ht="40" customHeight="1">
       <c r="A22" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.easygoing.ojousama.hit[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.ojousama.easygoing.hit[1]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
@@ -975,7 +975,7 @@
       </c>
       <c r="D22" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama.hit[1]</t>
+          <t xml:space="preserve">ojousama.easygoing.hit[1]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr" s="2">
@@ -992,7 +992,7 @@
     <row r="23" ht="40" customHeight="1">
       <c r="A23" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.easygoing.ojousama.hit[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.ojousama.easygoing.hit[2]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="D23" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama.hit[2]</t>
+          <t xml:space="preserve">ojousama.easygoing.hit[2]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr" s="2">
@@ -1024,7 +1024,7 @@
     <row r="24" ht="40" customHeight="1">
       <c r="A24" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.easygoing.ojousama.win[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.ojousama.easygoing.win[1]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="D24" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama.win[1]</t>
+          <t xml:space="preserve">ojousama.easygoing.win[1]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr" s="2">
@@ -1056,7 +1056,7 @@
     <row r="25" ht="40" customHeight="1">
       <c r="A25" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.easygoing.ojousama.win[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.ojousama.easygoing.win[2]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="D25" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama.win[2]</t>
+          <t xml:space="preserve">ojousama.easygoing.win[2]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr" s="2">
@@ -1088,7 +1088,7 @@
     <row r="26" ht="40" customHeight="1">
       <c r="A26" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="D26" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E26" t="inlineStr" s="2">
@@ -1120,7 +1120,7 @@
     <row r="27" ht="40" customHeight="1">
       <c r="A27" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="D27" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr" s="2">
@@ -1152,7 +1152,7 @@
     <row r="28" ht="40" customHeight="1">
       <c r="A28" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.easygoing.ojousama[3]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.ojousama.easygoing[3]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="D28" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[3]</t>
+          <t xml:space="preserve">ojousama.easygoing[3]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr" s="2">
@@ -1184,7 +1184,7 @@
     <row r="29" ht="40" customHeight="1">
       <c r="A29" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="D29" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E29" t="inlineStr" s="2">
@@ -1216,7 +1216,7 @@
     <row r="30" ht="40" customHeight="1">
       <c r="A30" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="D30" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr" s="2">
@@ -1248,7 +1248,7 @@
     <row r="31" ht="40" customHeight="1">
       <c r="A31" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.easygoing.ojousama[3]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.ojousama.easygoing[3]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="D31" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[3]</t>
+          <t xml:space="preserve">ojousama.easygoing[3]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr" s="2">
@@ -1280,7 +1280,7 @@
     <row r="32" ht="40" customHeight="1">
       <c r="A32" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="D32" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr" s="2">
@@ -1312,7 +1312,7 @@
     <row r="33" ht="40" customHeight="1">
       <c r="A33" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="D33" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr" s="2">
@@ -1344,7 +1344,7 @@
     <row r="34" ht="40" customHeight="1">
       <c r="A34" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.easygoing.ojousama[3]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.ojousama.easygoing[3]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="D34" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[3]</t>
+          <t xml:space="preserve">ojousama.easygoing[3]</t>
         </is>
       </c>
       <c r="E34" t="inlineStr" s="2">
@@ -1376,7 +1376,7 @@
     <row r="35" ht="40" customHeight="1">
       <c r="A35" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="D35" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr" s="2">
@@ -1408,7 +1408,7 @@
     <row r="36" ht="40" customHeight="1">
       <c r="A36" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="D36" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr" s="2">
@@ -1440,7 +1440,7 @@
     <row r="37" ht="40" customHeight="1">
       <c r="A37" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.easygoing.ojousama[3]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.ojousama.easygoing[3]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="D37" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[3]</t>
+          <t xml:space="preserve">ojousama.easygoing[3]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr" s="2">
@@ -1472,7 +1472,7 @@
     <row r="38" ht="40" customHeight="1">
       <c r="A38" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="D38" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E38" t="inlineStr" s="2">
@@ -1504,7 +1504,7 @@
     <row r="39" ht="40" customHeight="1">
       <c r="A39" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="D39" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E39" t="inlineStr" s="2">
@@ -1536,7 +1536,7 @@
     <row r="40" ht="40" customHeight="1">
       <c r="A40" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="D40" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E40" t="inlineStr" s="2">
@@ -1568,7 +1568,7 @@
     <row r="41" ht="40" customHeight="1">
       <c r="A41" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="D41" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr" s="2">
@@ -1600,7 +1600,7 @@
     <row r="42" ht="40" customHeight="1">
       <c r="A42" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="D42" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">loser.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E42" t="inlineStr" s="2">
@@ -1632,7 +1632,7 @@
     <row r="43" ht="40" customHeight="1">
       <c r="A43" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="D43" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">winner.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E43" t="inlineStr" s="2">
@@ -1664,7 +1664,7 @@
     <row r="44" ht="40" customHeight="1">
       <c r="A44" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="D44" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">loser.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E44" t="inlineStr" s="2">
@@ -1696,7 +1696,7 @@
     <row r="45" ht="40" customHeight="1">
       <c r="A45" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="D45" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">winner.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E45" t="inlineStr" s="2">
@@ -1728,7 +1728,7 @@
     <row r="46" ht="40" customHeight="1">
       <c r="A46" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="D46" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">attacker.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E46" t="inlineStr" s="2">
@@ -1760,7 +1760,7 @@
     <row r="47" ht="40" customHeight="1">
       <c r="A47" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="D47" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">defender.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E47" t="inlineStr" s="2">
@@ -1792,7 +1792,7 @@
     <row r="48" ht="40" customHeight="1">
       <c r="A48" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="D48" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">attacker.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E48" t="inlineStr" s="2">
@@ -1824,7 +1824,7 @@
     <row r="49" ht="40" customHeight="1">
       <c r="A49" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="D49" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">defender.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E49" t="inlineStr" s="2">
@@ -1856,7 +1856,7 @@
     <row r="50" ht="40" customHeight="1">
       <c r="A50" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="D50" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">attacker.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E50" t="inlineStr" s="2">
@@ -1888,7 +1888,7 @@
     <row r="51" ht="40" customHeight="1">
       <c r="A51" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="D51" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">defender.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr" s="2">
@@ -1920,7 +1920,7 @@
     <row r="52" ht="40" customHeight="1">
       <c r="A52" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="D52" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateAttacker.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">fateAttacker.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E52" t="inlineStr" s="2">
@@ -1952,7 +1952,7 @@
     <row r="53" ht="40" customHeight="1">
       <c r="A53" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="D53" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateDefender.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">fateDefender.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr" s="2">
@@ -1984,7 +1984,7 @@
     <row r="54" ht="40" customHeight="1">
       <c r="A54" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="D54" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">loserLines.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E54" t="inlineStr" s="2">
@@ -2016,7 +2016,7 @@
     <row r="55" ht="40" customHeight="1">
       <c r="A55" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="D55" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">winnerLines.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E55" t="inlineStr" s="2">
@@ -2048,7 +2048,7 @@
     <row r="56" ht="40" customHeight="1">
       <c r="A56" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="D56" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateLoser.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">fateLoser.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E56" t="inlineStr" s="2">
@@ -2080,7 +2080,7 @@
     <row r="57" ht="40" customHeight="1">
       <c r="A57" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="D57" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateWinner.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">fateWinner.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr" s="2">
@@ -2112,7 +2112,7 @@
     <row r="58" ht="40" customHeight="1">
       <c r="A58" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="D58" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">loser.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr" s="2">
@@ -2144,7 +2144,7 @@
     <row r="59" ht="40" customHeight="1">
       <c r="A59" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="D59" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">winner.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E59" t="inlineStr" s="2">
@@ -2176,7 +2176,7 @@
     <row r="60" ht="40" customHeight="1">
       <c r="A60" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="D60" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">loserLines.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E60" t="inlineStr" s="2">
@@ -2208,7 +2208,7 @@
     <row r="61" ht="40" customHeight="1">
       <c r="A61" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="D61" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">winnerLines.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E61" t="inlineStr" s="2">
@@ -3008,7 +3008,7 @@
     <row r="86" ht="40" customHeight="1">
       <c r="A86" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="2">
@@ -3023,7 +3023,7 @@
       </c>
       <c r="D86" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">accepted.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E86" t="inlineStr" s="2">
@@ -3040,7 +3040,7 @@
     <row r="87" ht="40" customHeight="1">
       <c r="A87" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="2">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="D87" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">defended.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr" s="2">
@@ -3072,7 +3072,7 @@
     <row r="88" ht="40" customHeight="1">
       <c r="A88" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="D88" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">defense_failed.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr" s="2">
@@ -3104,7 +3104,7 @@
     <row r="89" ht="40" customHeight="1">
       <c r="A89" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.former_champ.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.former_champ.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="D89" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">former_champ.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">former_champ.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr" s="2">
@@ -3136,7 +3136,7 @@
     <row r="90" ht="40" customHeight="1">
       <c r="A90" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="D90" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">accept_terminal.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr" s="2">
@@ -3168,7 +3168,7 @@
     <row r="91" ht="40" customHeight="1">
       <c r="A91" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="D91" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">refuse_champ.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr" s="2">
@@ -3200,7 +3200,7 @@
     <row r="92" ht="40" customHeight="1">
       <c r="A92" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="D92" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">A1_champion.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E92" t="inlineStr" s="2">
@@ -3232,7 +3232,7 @@
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A2_uncrowned.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">A2_uncrowned.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E93" t="inlineStr" s="2">
@@ -3264,7 +3264,7 @@
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A3_heel.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">A3_heel.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr" s="2">
@@ -3296,7 +3296,7 @@
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A4_veteran.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">A4_veteran.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr" s="2">
@@ -3328,7 +3328,7 @@
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B1_young.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1_young.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">B1_young.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr" s="2">
@@ -3360,7 +3360,7 @@
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3375,7 +3375,7 @@
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_prime.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">B2_prime.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr" s="2">
@@ -3392,7 +3392,7 @@
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B3_older.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3_older.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">B3_older.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr" s="2">
@@ -3424,7 +3424,7 @@
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_champion_injury.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">B4_champion_injury.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr" s="2">
@@ -3456,7 +3456,7 @@
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr" s="2">
@@ -3488,7 +3488,7 @@
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">raise_accept.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="2">
@@ -3520,7 +3520,7 @@
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr" s="2">
@@ -3552,7 +3552,7 @@
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr" s="2">
@@ -3584,7 +3584,7 @@
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">raise_open.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="2">
@@ -3616,7 +3616,7 @@
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">raise_refuse.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
@@ -3648,7 +3648,7 @@
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">sudden_departure.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="2">
@@ -3673,14 +3673,14 @@
       </c>
       <c r="F106" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">聞いてくださるの？ そうねえ……{record}なんだか、代わり映えしなくて。新しいことがしてみたいの。</t>
+          <t xml:space="preserve">まあ、とうとうこの日が参りましたのね。では、お元気で。</t>
         </is>
       </c>
     </row>
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3695,7 +3695,7 @@
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">sudden_departure.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
@@ -3705,14 +3705,14 @@
       </c>
       <c r="F107" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、あのね。{tenure}いろいろ考えたのだけれど……環境を変えてみようかしら、と。</t>
+          <t xml:space="preserve">そろそろ潮時かしら。楽しゅうございました、ええ。ごきげんよう。</t>
         </is>
       </c>
     </row>
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">transfer_listen.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="2">
@@ -3737,14 +3737,14 @@
       </c>
       <c r="F108" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いやはや社長。言いにくいのだけれど。{tenure}少し外の風に当たってみたくなって。</t>
+          <t xml:space="preserve">聞いてくださるの？ そうねえ……{record}なんだか、代わり映えしなくて。新しいことがしてみたいの。</t>
         </is>
       </c>
     </row>
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">transfer_open.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="2">
@@ -3769,14 +3769,14 @@
       </c>
       <c r="F109" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、まあそうなりますわよね。{tenure_farewell}{rivalry}どうか、お元気で。</t>
+          <t xml:space="preserve">社長、あのね。{tenure}いろいろ考えたのだけれど……環境を変えてみようかしら、と。</t>
         </is>
       </c>
     </row>
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">transfer_open.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="2">
@@ -3801,14 +3801,14 @@
       </c>
       <c r="F110" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ごめんなさい社長……。お金の話ではないの。もう、心が決まってしまったから。</t>
+          <t xml:space="preserve">いやはや社長。言いにくいのだけれど。{tenure}少し外の風に当たってみたくなって。</t>
         </is>
       </c>
     </row>
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">transfer_release.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
@@ -3833,14 +3833,14 @@
       </c>
       <c r="F111" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、そこまでしてくださるの？ ……では、もう少しだけ居させていただこうかしら。</t>
+          <t xml:space="preserve">ふふ、まあそうなりますわよね。{tenure_farewell}{rivalry}どうか、お元気で。</t>
         </is>
       </c>
     </row>
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="C112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">start.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">transfer_retain_fail.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
@@ -3865,93 +3865,93 @@
       </c>
       <c r="F112" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">条件をお聞かせくださいまし。それ次第ですわ</t>
+          <t xml:space="preserve">ごめんなさい社長……。お金の話ではないの。もう、心が決まってしまったから。</t>
         </is>
       </c>
     </row>
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[1]</t>
+          <t xml:space="preserve">transfer_retain_success.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F113" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、向こうのお茶会のほうが、わたくしの性に合っておりますの。</t>
+          <t xml:space="preserve">あら、そこまでしてくださるの？ ……では、もう少しだけ居させていただこうかしら。</t>
         </is>
       </c>
     </row>
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[1]</t>
+          <t xml:space="preserve">start.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、そんな昔のこと、もう忘れていますわよ。</t>
+          <t xml:space="preserve">条件をお聞かせくださいまし。それ次第ですわ</t>
         </is>
       </c>
     </row>
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F07_LEADER_LINES.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F07_LEADER_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -3961,14 +3961,14 @@
       </c>
       <c r="F115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、気安いところで申し上げますけれど、待遇、もう少しどうにか。</t>
+          <t xml:space="preserve">社長〜、わたくしたちのこと、たまには思い出してくださってもよろしくてよ?</t>
         </is>
       </c>
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -3978,29 +3978,29 @@
       </c>
       <c r="C116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近絶好調ですわ！ もっと上に行けそうですの</t>
+          <t xml:space="preserve">社長〜、次のメインカード、わたくしたちでいかがかしら?</t>
         </is>
       </c>
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4010,29 +4010,29 @@
       </c>
       <c r="C117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、もうこれ以上は？ まあ、十分ですわ</t>
+          <t xml:space="preserve">社長〜、お給金の件、少々考えてくださってもよろしくてよ?</t>
         </is>
       </c>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4042,29 +4042,29 @@
       </c>
       <c r="C118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来れるとは思いませんでしたわ！</t>
+          <t xml:space="preserve">社長〜、わたくしたちの働き、たまには褒めてくださってもよろしくてよ?</t>
         </is>
       </c>
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4074,29 +4074,29 @@
       </c>
       <c r="C119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">順調に成長してますわ♪</t>
+          <t xml:space="preserve">まあ嬉しい、社長ありがとうございますわ〜。</t>
         </is>
       </c>
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4106,29 +4106,29 @@
       </c>
       <c r="C120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらまあ…とんでもないところまで来てしまいましたわ</t>
+          <t xml:space="preserve">あら、そうですの。お時間取らせてしまいましたわね〜。</t>
         </is>
       </c>
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4138,29 +4138,29 @@
       </c>
       <c r="C121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_growth.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F121" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンの方が増えて嬉しいですわ！</t>
+          <t xml:space="preserve">あら、別の形ですの? まあ、ありがたいですわ〜。</t>
         </is>
       </c>
     </row>
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4170,29 +4170,29 @@
       </c>
       <c r="C122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F122" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、こんなに！ もっともっと楽しんでまいりましょう！</t>
+          <t xml:space="preserve">まあ嬉しい、社長ありがとう! 華やかなメインにいたしますわ。</t>
         </is>
       </c>
     </row>
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4202,29 +4202,29 @@
       </c>
       <c r="C123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F123" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">少しやる気が出ませんの…でも頑張りますわ</t>
+          <t xml:space="preserve">まあ、つれないですこと。次は期待してますわ〜。</t>
         </is>
       </c>
     </row>
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4234,29 +4234,29 @@
       </c>
       <c r="C124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F124" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やる気が戻ってまいりましたわ！ もう大丈夫ですの</t>
+          <t xml:space="preserve">あら、そういう形ですの? まあ、ありがとうございますわ〜。</t>
         </is>
       </c>
     </row>
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4266,29 +4266,29 @@
       </c>
       <c r="C125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F125" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">調子が戻ってまいりましたわ！ もう大丈夫ですの</t>
+          <t xml:space="preserve">まあ嬉しい! 社長ありがとうございますわ〜。</t>
         </is>
       </c>
     </row>
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4298,29 +4298,29 @@
       </c>
       <c r="C126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F126" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近少し不調ですの…でもすぐ立て直しますわ</t>
+          <t xml:space="preserve">あら、そうですの。まあ仕方ありませんわ〜。</t>
         </is>
       </c>
     </row>
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -4330,29 +4330,29 @@
       </c>
       <c r="C127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F127" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の試合でしたわ！ お相手にも感謝ですの</t>
+          <t xml:space="preserve">あら、お金じゃない形ですの? まあ、それも素敵ですわね。</t>
         </is>
       </c>
     </row>
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4362,29 +4362,29 @@
       </c>
       <c r="C128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F128" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一年間お守りいたしましたわ。来年もこの座を守りますの</t>
+          <t xml:space="preserve">まあ嬉しい、社長に褒められちゃいましたわ〜!</t>
         </is>
       </c>
     </row>
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4394,29 +4394,29 @@
       </c>
       <c r="C129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F129" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">殿堂入りですの…！ 夢のようですわ…</t>
+          <t xml:space="preserve">あら、つれないですこと。まあいいですわ〜。</t>
         </is>
       </c>
     </row>
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4426,29 +4426,29 @@
       </c>
       <c r="C130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVPですの！ 光栄ですわ。来年も精進いたしますの</t>
+          <t xml:space="preserve">あら、別の形ですの? まあ、ありがたいですわ〜。</t>
         </is>
       </c>
     </row>
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4458,29 +4458,29 @@
       </c>
       <c r="C131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ…！ 新人王ですの…！ 光栄ですわ</t>
+          <t xml:space="preserve">あら、気にしてらしたの? 次はお誘いしますわ〜。</t>
         </is>
       </c>
     </row>
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4490,29 +4490,29 @@
       </c>
       <c r="C132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、ドームですのね。なんだか楽しそうですわ</t>
+          <t xml:space="preserve">ありがとうございますわ〜、楽しんで参りますわ。</t>
         </is>
       </c>
     </row>
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4522,29 +4522,29 @@
       </c>
       <c r="C133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[2]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ気楽にいきますわよ、ほほほ</t>
+          <t xml:space="preserve">あら、配慮が足りませんでしたわね〜。気をつけますわ。</t>
         </is>
       </c>
     </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.easygoing.ojousama[3]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4554,29 +4554,29 @@
       </c>
       <c r="C134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[3]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こういう大きな会場、わたくし嫌いじゃありませんの</t>
+          <t xml:space="preserve">ありがとうございますわ〜。</t>
         </is>
       </c>
     </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4586,29 +4586,29 @@
       </c>
       <c r="C135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ、満員ですのね! 嬉しゅうございますわ</t>
+          <t xml:space="preserve">あら、見られてましたの? では控えますわ〜。</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4618,29 +4618,29 @@
       </c>
       <c r="C136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[2]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなに楽しい日は、なかなかありませんの</t>
+          <t xml:space="preserve">まあ、ご理解ありがとうございますわ〜。続けますわよ。</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.easygoing.ojousama[3]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4650,29 +4650,29 @@
       </c>
       <c r="C137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[3]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ほほほ、またやりたくなりますわ</t>
+          <t xml:space="preserve">あら、ばれてましたの? 明日から出ますわ〜。</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4682,29 +4682,29 @@
       </c>
       <c r="C138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンの皆さまに、もっと近くで見ていただきたいんです</t>
+          <t xml:space="preserve">まあ、見逃してくださるの? 助かりますわ〜。</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4714,29 +4714,29 @@
       </c>
       <c r="C139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">テレビ…！わたくし、出てみたいです</t>
+          <t xml:space="preserve">あら、メンバー優先ですの? まあ、ありがたいですわ〜。</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4746,29 +4746,29 @@
       </c>
       <c r="C140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.accept.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、成功いたしましたの!わたくし、嬉しくて仕方ありませんわ!</t>
+          <t xml:space="preserve">まあ、見ていてくださったの? ではお言葉に甘えますわ〜。</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4778,29 +4778,29 @@
       </c>
       <c r="C141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うふふ、ご一緒に楽しくやりましょうよ</t>
+          <t xml:space="preserve">まあ、まだ大丈夫ですのよ〜。</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4810,29 +4810,29 @@
       </c>
       <c r="C142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[2]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">退屈なプロレスはしないと約束いたしますわ</t>
+          <t xml:space="preserve">あら、皆のケアですの? 助かりますわ〜。</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4842,29 +4842,29 @@
       </c>
       <c r="C143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、よろしくお願いしますわぁ</t>
+          <t xml:space="preserve">あら、そんな話してましたの? 注意しておきますわ〜。</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4874,29 +4874,29 @@
       </c>
       <c r="C144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[2]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お仲間入りですわね。よろしくですの</t>
+          <t xml:space="preserve">ありがとうございますわ〜。穏便に、ですわね。</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4906,29 +4906,29 @@
       </c>
       <c r="C145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ごきげんよう。新天地ですわ、暴れさせていただきますの</t>
+          <t xml:space="preserve">あら、別ルートですの? 下の子のフォロー、お願いいたしますわ〜。</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4938,29 +4938,29 @@
       </c>
       <c r="C146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[2]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここなら好きにやれそうですわね。楽しみですの</t>
+          <t xml:space="preserve">あら、見られてましたの? 失礼いたしましたわ〜。</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -4970,29 +4970,29 @@
       </c>
       <c r="C147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、今日から仲間ですわね。よろしくお願いしますの</t>
+          <t xml:space="preserve">（あら、と微笑んで、お話を流しましたわ）</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5002,29 +5002,29 @@
       </c>
       <c r="C148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[2]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">皆様、楽しくやりましょうね</t>
+          <t xml:space="preserve">あら、別の手立てですの? ありがたいですわ〜。</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5034,29 +5034,29 @@
       </c>
       <c r="C149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらあら…少し休みますわね</t>
+          <t xml:space="preserve">あら、見ていらしたの? では緩めますわ〜。</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5066,29 +5066,29 @@
       </c>
       <c r="C150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うふふ、ご一緒に楽しくやりましょうよ</t>
+          <t xml:space="preserve">まあ、続けていいんですの? ありがとうございますわ〜。</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5098,29 +5098,29 @@
       </c>
       <c r="C151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">退屈なプロレスはしないと約束いたしますわ</t>
+          <t xml:space="preserve">あら、わたくしより皆優先ですの? ありがたいですわ〜。</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.easygoing.attack.ojousama</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5130,29 +5130,29 @@
       </c>
       <c r="C152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">easygoing.attack.ojousama</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、よろしくお願いしますわぁ</t>
+          <t xml:space="preserve">仲良しごっこは、もう終わりですわね</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.easygoing.defend.ojousama</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5162,61 +5162,61 @@
       </c>
       <c r="C153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">easygoing.defend.ojousama</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お仲間入りですわね。よろしくですの</t>
+          <t xml:space="preserve">まあ、仕方ありませんわね</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES</t>
         </is>
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">巡り巡って、良い場所にご縁がありましたこと</t>
+          <t xml:space="preserve">あら、そんな昔のこと、もう忘れていますわよ。</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5226,29 +5226,29 @@
       </c>
       <c r="C155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ごきげんよう。新天地ですわ、暴れさせていただきますの</t>
+          <t xml:space="preserve">最近絶好調ですわ！ もっと上に行けそうですの</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5258,29 +5258,29 @@
       </c>
       <c r="C156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">cap_reached.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここなら好きにやれそうですわね。楽しみですの</t>
+          <t xml:space="preserve">あら、もうこれ以上は？ まあ、十分ですわ</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5290,29 +5290,29 @@
       </c>
       <c r="C157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">ovr_elite.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、今日から仲間ですわね。よろしくお願いしますの</t>
+          <t xml:space="preserve">ここまで来れるとは思いませんでしたわ！</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5322,29 +5322,29 @@
       </c>
       <c r="C158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">ovr_growth.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">皆様、楽しくやりましょうね</t>
+          <t xml:space="preserve">順調に成長してますわ♪</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5354,29 +5354,29 @@
       </c>
       <c r="C159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">ovr_legend.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらあら…少し休みますわね</t>
+          <t xml:space="preserve">あらまあ…とんでもないところまで来てしまいましたわ</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5386,29 +5386,29 @@
       </c>
       <c r="C160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">pop_growth.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、こういうこともありますわね。ごきげんよう</t>
+          <t xml:space="preserve">ファンの方が増えて嬉しいですわ！</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5418,29 +5418,29 @@
       </c>
       <c r="C161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">pop_star.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お邪魔いたしますわ。短い間ですけれど、暴れさせていただきますの</t>
+          <t xml:space="preserve">まあ、こんなに！ もっともっと楽しんでまいりましょう！</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5450,29 +5450,29 @@
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一時のご縁ですもの、思い切りやらせていただきますわ</t>
+          <t xml:space="preserve">少しやる気が出ませんの…でも頑張りますわ</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5482,29 +5482,29 @@
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うふふ♪見出されるって、とても気分がよいことですね</t>
+          <t xml:space="preserve">やる気が戻ってまいりましたわ！ もう大丈夫ですの</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5514,29 +5514,29 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は負けてしまいましたけれど…次はもっとよい試合をしますわ</t>
+          <t xml:space="preserve">調子が戻ってまいりましたわ！ もう大丈夫ですの</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5546,29 +5546,29 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">defeat.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいですけれど、俯いていては応援してくださる方に失礼ですもの</t>
+          <t xml:space="preserve">最近少し不調ですの…でもすぐ立て直しますわ</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5578,29 +5578,29 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">bestMatch.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンはわたくしですの。また守り切りましたわ</t>
+          <t xml:space="preserve">最高の試合でしたわ！ お相手にも感謝ですの</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5610,29 +5610,29 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">champion.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よい試合でしたわ。またいつでも挑んでらして</t>
+          <t xml:space="preserve">一年間お守りいたしましたわ。来年もこの座を守りますの</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5642,29 +5642,29 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">hallOfFame.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けてしまいましたわ…でも応援してくださる方がいる限り、立ち上がりますの</t>
+          <t xml:space="preserve">殿堂入りですの…！ 夢のようですわ…</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5674,29 +5674,29 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">mvp.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ベルトのないわたくしなんて想像もできませんでしたわ。でも、わたくしはわたくしですもの</t>
+          <t xml:space="preserve">MVPですの！ 光栄ですわ。来年も精進いたしますの</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5706,29 +5706,29 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">rookie.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">新チャンピオン誕生ですわ。ここからもっと盛り上げますの</t>
+          <t xml:space="preserve">まあ…！ 新人王ですの…！ 光栄ですわ</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5738,29 +5738,29 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルト、獲ってしまいましたわ。最高の気分ですの</t>
+          <t xml:space="preserve">あら、ドームですのね。なんだか楽しそうですわ</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5770,29 +5770,29 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、こういうこともありますわね。ごきげんよう</t>
+          <t xml:space="preserve">まぁ気楽にいきますわよ、ほほほ</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.easygoing[3]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5802,29 +5802,29 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.easygoing[3]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お邪魔いたしますわ。短い間ですけれど、暴れさせていただきますの</t>
+          <t xml:space="preserve">こういう大きな会場、わたくし嫌いじゃありませんの</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5834,29 +5834,29 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一時のご縁ですもの、思い切りやらせていただきますわ</t>
+          <t xml:space="preserve">まぁ、満員ですのね! 嬉しゅうございますわ</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5866,29 +5866,29 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は負けてしまいましたけれど…次はもっとよい試合をしますわ</t>
+          <t xml:space="preserve">こんなに楽しい日は、なかなかありませんの</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.easygoing[3]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5898,29 +5898,29 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.easygoing[3]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいですけれど、俯いていては応援してくださる方に失礼ですもの</t>
+          <t xml:space="preserve">ほほほ、またやりたくなりますわ</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5930,29 +5930,29 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[1]</t>
+          <t xml:space="preserve">E1.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンはわたくしですの。また守り切りましたわ</t>
+          <t xml:space="preserve">ファンの皆さまに、もっと近くで見ていただきたいんです</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -5962,29 +5962,29 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[2]</t>
+          <t xml:space="preserve">E1.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よい試合でしたわ。またいつでも挑んでらして</t>
+          <t xml:space="preserve">テレビ…！わたくし、出てみたいです</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -5994,29 +5994,29 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[1]</t>
+          <t xml:space="preserve">E1.accept.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けてしまいましたわ…でも応援してくださる方がいる限り、立ち上がりますの</t>
+          <t xml:space="preserve">まあ、成功いたしましたの!わたくし、嬉しくて仕方ありませんわ!</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
@@ -6041,14 +6041,14 @@
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ベルトのないわたくしなんて想像もできませんでしたわ。でも、わたくしはわたくしですもの</t>
+          <t xml:space="preserve">うふふ、ご一緒に楽しくやりましょうよ</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
@@ -6073,14 +6073,14 @@
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">新チャンピオン誕生ですわ。ここからもっと盛り上げますの</t>
+          <t xml:space="preserve">退屈なプロレスはしないと約束いたしますわ</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6090,12 +6090,12 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -6105,14 +6105,14 @@
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルト、獲ってしまいましたわ。最高の気分ですの</t>
+          <t xml:space="preserve">ふふ、よろしくお願いしますわぁ</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6122,29 +6122,29 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">う〜ん…少々、合いませんかしら…</t>
+          <t xml:space="preserve">お仲間入りですわね。よろしくですの</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6154,29 +6154,29 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、近ごろ少し素っ気ないような</t>
+          <t xml:space="preserve">ごきげんよう。新天地ですわ、暴れさせていただきますの</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6186,29 +6186,29 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">はて…空気が微かに変わりましたかしら</t>
+          <t xml:space="preserve">ここなら好きにやれそうですわね。楽しみですの</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6218,29 +6218,29 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しくお過ごしできますの〜</t>
+          <t xml:space="preserve">まあ、今日から仲間ですわね。よろしくお願いしますの</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6250,29 +6250,29 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の相方。ずっとこのままでいたいものです</t>
+          <t xml:space="preserve">皆様、楽しくやりましょうね</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6282,29 +6282,29 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒にいると、何もかも上手く回る気がして</t>
+          <t xml:space="preserve">あらあら…少し休みますわね</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6314,29 +6314,29 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">draftInterest.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">熱い間柄も一区切り。少し寂しいものです</t>
+          <t xml:space="preserve">うふふ、ご一緒に楽しくやりましょうよ</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6346,29 +6346,29 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">draftInterest.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ、因縁とて永遠ではありませんもの〜</t>
+          <t xml:space="preserve">退屈なプロレスはしないと約束いたしますわ</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6378,29 +6378,29 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">draftJoin.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">良い勝負になりそうです〜。少し燃えてきました</t>
+          <t xml:space="preserve">ふふ、よろしくお願いしますわぁ</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6410,29 +6410,29 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">draftJoin.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うふふ、負けたくありませんね</t>
+          <t xml:space="preserve">お仲間入りですわね。よろしくですの</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6442,29 +6442,29 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">faGreeting.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">本気でやり合いたい相手など、そういません</t>
+          <t xml:space="preserve">巡り巡って、良い場所にご縁がありましたこと</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6474,29 +6474,29 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">faSigning.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うふふ、思い浮かべるだけで力が入ります</t>
+          <t xml:space="preserve">ごきげんよう。新天地ですわ、暴れさせていただきますの</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6506,29 +6506,29 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">faSigning.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この試合が一番楽しい。ずっとこのままであればよいのに</t>
+          <t xml:space="preserve">ここなら好きにやれそうですわね。楽しみですの</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6538,29 +6538,29 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">faWelcome.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">運命の好敵手…そう呼びたくなります</t>
+          <t xml:space="preserve">まあ、今日から仲間ですわね。よろしくお願いしますの</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6570,29 +6570,29 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">faWelcome.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここは素晴らしい〜。皆さんとやるのが楽しくて</t>
+          <t xml:space="preserve">皆様、楽しくやりましょうね</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6602,29 +6602,29 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">injury.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体、とても居心地がよいのです〜</t>
+          <t xml:space="preserve">あらあら…少し休みますわね</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6634,29 +6634,29 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">release.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">さすがにこれは…笑えません</t>
+          <t xml:space="preserve">ふふ、こういうこともありますわね。ごきげんよう</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6666,29 +6666,29 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">rentalGreeting.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うふふ…と笑っている場合ではありませんね、これは</t>
+          <t xml:space="preserve">お邪魔いたしますわ。短い間ですけれど、暴れさせていただきますの</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6698,29 +6698,29 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">rentalGreeting.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">う〜ん…近ごろ少し胸がすっきりしません…</t>
+          <t xml:space="preserve">一時のご縁ですもの、思い切りやらせていただきますわ</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6730,29 +6730,29 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">scoutGreeting.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ大丈夫…ですよね？ 少し不安ですけれど</t>
+          <t xml:space="preserve">うふふ♪見出されるって、とても気分がよいことですね</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6762,29 +6762,29 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">連勝が止まりましたわ…でもまた頑張りますの</t>
+          <t xml:space="preserve">今日は負けてしまいましたけれど…次はもっとよい試合をしますわ</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6794,29 +6794,29 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">傷だらけですけれど、最後まで来てしまいましたわ。ふふ、やるしかありませんわね</t>
+          <t xml:space="preserve">悔しいですけれど、俯いていては応援してくださる方に失礼ですもの</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6826,29 +6826,29 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">titleDefense.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">さすがに身体が重いですの。でも、締めくくりは楽しませていただきますわ</t>
+          <t xml:space="preserve">チャンピオンはわたくしですの。また守り切りましたわ</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6858,29 +6858,29 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">titleDefense.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、お相手はどなた? 次から次へと、賑やかですこと</t>
+          <t xml:space="preserve">よい試合でしたわ。またいつでも挑んでらして</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6890,29 +6890,29 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">titleLoss.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">賑やかな一日になりそうですわね。…面白いですわ</t>
+          <t xml:space="preserve">負けてしまいましたわ…でも応援してくださる方がいる限り、立ち上がりますの</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6922,29 +6922,29 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">titleLoss.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、お見送りしましたわ。…ふぅ、まだ立っていますのよ。次はどなた?</t>
+          <t xml:space="preserve">…ベルトのないわたくしなんて想像もできませんでしたわ。でも、わたくしはわたくしですもの</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6954,29 +6954,29 @@
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">titleWin.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、まだ終わりませんの? いいですわ、次の方、いらして</t>
+          <t xml:space="preserve">新チャンピオン誕生ですわ。ここからもっと盛り上げますの</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -6986,29 +6986,29 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">titleWin.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">素敵な三人でしたわ。この勝利は、お二人と分かち合いたいですの</t>
+          <t xml:space="preserve">ベルト、獲ってしまいましたわ。最高の気分ですの</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7018,29 +7018,29 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お二人がいてくださったから、安心して戦えましたわ。ふふ</t>
+          <t xml:space="preserve">ふふ、こういうこともありますわね。ごきげんよう</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7050,29 +7050,29 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お賞はありがたいですわ。でも……お一人で笑うのは、趣味じゃありませんの</t>
+          <t xml:space="preserve">お邪魔いたしますわ。短い間ですけれど、暴れさせていただきますの</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7082,29 +7082,29 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次はお三人で勝って、優雅に乾杯したいですわね</t>
+          <t xml:space="preserve">一時のご縁ですもの、思い切りやらせていただきますわ</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7114,29 +7114,29 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次から次へと来るのですもの。退屈しませんでしたわ。身体は少し重いですけれど</t>
+          <t xml:space="preserve">今日は負けてしまいましたけれど…次はもっとよい試合をしますわ</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7146,29 +7146,29 @@
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人お相手したのかしら。まあ、全員お見送りしましたし、よろしいですわね</t>
+          <t xml:space="preserve">悔しいですけれど、俯いていては応援してくださる方に失礼ですもの</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7178,29 +7178,29 @@
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、優勝ですの！ 最高ですわ〜！</t>
+          <t xml:space="preserve">チャンピオンはわたくしですの。また守り切りましたわ</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7210,29 +7210,29 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やりましたわ〜！ ご褒美が楽しみですわね</t>
+          <t xml:space="preserve">よい試合でしたわ。またいつでも挑んでらして</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7242,29 +7242,29 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やりましたわ。この調子で行きますわよ</t>
+          <t xml:space="preserve">負けてしまいましたわ…でも応援してくださる方がいる限り、立ち上がりますの</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7274,29 +7274,29 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだまだ楽しめそうですわね</t>
+          <t xml:space="preserve">…ベルトのないわたくしなんて想像もできませんでしたわ。でも、わたくしはわたくしですもの</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7306,29 +7306,29 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、決勝まで来ちゃいましたわ。楽しみですわね</t>
+          <t xml:space="preserve">新チャンピオン誕生ですわ。ここからもっと盛り上げますの</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7338,29 +7338,29 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最後の一戦！ 思いっきりやりますわよ</t>
+          <t xml:space="preserve">ベルト、獲ってしまいましたわ。最高の気分ですの</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7370,29 +7370,29 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">bond_39_down.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">さあ、楽しい時間の始まりですわ</t>
+          <t xml:space="preserve">う〜ん…少々、合いませんかしら…</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7402,29 +7402,29 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">bond_59_down.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">気楽に参りましょう。でも負けませんわよ</t>
+          <t xml:space="preserve">あら、近ごろ少し素っ気ないような</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7434,29 +7434,29 @@
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">bond_59_down.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、わたくしも呼ばれましたの？ 面白そうですわね</t>
+          <t xml:space="preserve">はて…空気が微かに変わりましたかしら</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7466,29 +7466,29 @@
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">bond_60_up.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしが選ばれないわけがありませんわよね</t>
+          <t xml:space="preserve">楽しくお過ごしできますの〜</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7498,29 +7498,29 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[1]</t>
+          <t xml:space="preserve">bond_80_up.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力で参りますわ！ よろしくお願いいたしますの</t>
+          <t xml:space="preserve">最高の相方。ずっとこのままでいたいものです</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7530,29 +7530,29 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[1]</t>
+          <t xml:space="preserve">bond_80_up.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、勝っちゃいましたわ!最高の舞台で、最高の気分ですの!</t>
+          <t xml:space="preserve">一緒にいると、何もかも上手く回る気がして</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7562,29 +7562,29 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[1]</t>
+          <t xml:space="preserve">rivalry_29_down.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら〜、面白そうな団体ですわね。遊ばせていただきますわ</t>
+          <t xml:space="preserve">熱い間柄も一区切り。少し寂しいものです</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7594,29 +7594,29 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[2]</t>
+          <t xml:space="preserve">rivalry_29_down.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしたちと勝負しません？ きっと楽しいですわよ</t>
+          <t xml:space="preserve">まぁ、因縁とて永遠ではありませんもの〜</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7626,29 +7626,29 @@
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[1]</t>
+          <t xml:space="preserve">rivalry_30_up.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら〜、お断りですの？ もったいないですわ</t>
+          <t xml:space="preserve">良い勝負になりそうです〜。少し燃えてきました</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7658,29 +7658,29 @@
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[2]</t>
+          <t xml:space="preserve">rivalry_30_up.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、いいですわ。またの機会にいたしましょう</t>
+          <t xml:space="preserve">うふふ、負けたくありませんね</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7690,29 +7690,29 @@
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">rivalry_50_up.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらあら、負けてしまいましたわ。でもくよくよしませんわ</t>
+          <t xml:space="preserve">本気でやり合いたい相手など、そういません</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7722,29 +7722,29 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">rivalry_50_up.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次はもっと上手くやりますわよ〜</t>
+          <t xml:space="preserve">うふふ、思い浮かべるだけで力が入ります</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7754,29 +7754,29 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">rivalry_70_up.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やりましたわ〜！ 勝利ですわ！</t>
+          <t xml:space="preserve">この試合が一番楽しい。ずっとこのままであればよいのに</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7786,29 +7786,29 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">rivalry_70_up.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しい対抗戦でしたわ。またぜひ</t>
+          <t xml:space="preserve">運命の好敵手…そう呼びたくなります</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7818,29 +7818,29 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[1]</t>
+          <t xml:space="preserve">trust_above_75.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、勝ってしまいましたわ～。うちの団体、なかなかやりますでしょ？</t>
+          <t xml:space="preserve">ここは素晴らしい〜。皆さんとやるのが楽しくて</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7850,29 +7850,29 @@
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[2]</t>
+          <t xml:space="preserve">trust_above_75.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらあら、勝っちゃいましたわね〜</t>
+          <t xml:space="preserve">この団体、とても居心地がよいのです〜</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.easygoing.ojousama[3]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7882,29 +7882,29 @@
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[3]</t>
+          <t xml:space="preserve">trust_below_20.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しかったですわ〜。またやりましょうね</t>
+          <t xml:space="preserve">さすがにこれは…笑えません</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7914,29 +7914,29 @@
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">trust_below_20.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最後まで楽しゅうございましたわ。ありがとうございます</t>
+          <t xml:space="preserve">うふふ…と笑っている場合ではありませんね、これは</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7946,29 +7946,29 @@
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.ojousama[1]</t>
+          <t xml:space="preserve">trust_below_35.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">巡り巡って、良い場所にご縁がありましたこと</t>
+          <t xml:space="preserve">う〜ん…近ごろ少し胸がすっきりしません…</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -7978,27 +7978,1275 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_below_35.easygoing.ojousama[2]</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まぁ大丈夫…ですよね？ 少し不安ですけれど</t>
+        </is>
+      </c>
+    </row>
+    <row r="242" ht="40" customHeight="1">
+      <c r="A242" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">連勝が止まりましたわ…でもまた頑張りますの</t>
+        </is>
+      </c>
+    </row>
+    <row r="243" ht="40" customHeight="1">
+      <c r="A243" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">傷だらけですけれど、最後まで来てしまいましたわ。ふふ、やるしかありませんわね</t>
+        </is>
+      </c>
+    </row>
+    <row r="244" ht="40" customHeight="1">
+      <c r="A244" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.ojousama.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.ojousama.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">さすがに身体が重いですの。でも、締めくくりは楽しませていただきますわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" ht="40" customHeight="1">
+      <c r="A245" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あら、お相手はどなた? 次から次へと、賑やかですこと</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" ht="40" customHeight="1">
+      <c r="A246" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.ojousama.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.ojousama.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">賑やかな一日になりそうですわね。…面白いですわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="40" customHeight="1">
+      <c r="A247" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">survivor.ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">一人、お見送りしましたわ。…ふぅ、まだ立っていますのよ。次はどなた?</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="40" customHeight="1">
+      <c r="A248" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.ojousama.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">survivor.ojousama.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あら、まだ終わりませんの? いいですわ、次の方、いらして</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="40" customHeight="1">
+      <c r="A249" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">素敵な三人でしたわ。この勝利は、お二人と分かち合いたいですの</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="40" customHeight="1">
+      <c r="A250" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.ojousama.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.ojousama.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">お二人がいてくださったから、安心して戦えましたわ。ふふ</t>
+        </is>
+      </c>
+    </row>
+    <row r="251" ht="40" customHeight="1">
+      <c r="A251" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">defiant.ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">お賞はありがたいですわ。でも……お一人で笑うのは、趣味じゃありませんの</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="40" customHeight="1">
+      <c r="A252" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.ojousama.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">defiant.ojousama.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">次はお三人で勝って、優雅に乾杯したいですわね</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" ht="40" customHeight="1">
+      <c r="A253" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">次から次へと来るのですもの。退屈しませんでしたわ。身体は少し重いですけれど</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" ht="40" customHeight="1">
+      <c r="A254" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.ojousama.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.ojousama.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">何人お相手したのかしら。まあ、全員お見送りしましたし、よろしいですわね</t>
+        </is>
+      </c>
+    </row>
+    <row r="255" ht="40" customHeight="1">
+      <c r="A255" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まあ、優勝ですの！ 最高ですわ〜！</t>
+        </is>
+      </c>
+    </row>
+    <row r="256" ht="40" customHeight="1">
+      <c r="A256" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.ojousama.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.ojousama.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">やりましたわ〜！ ご褒美が楽しみですわね</t>
+        </is>
+      </c>
+    </row>
+    <row r="257" ht="40" customHeight="1">
+      <c r="A257" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postMatchWin.ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">やりましたわ。この調子で行きますわよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="258" ht="40" customHeight="1">
+      <c r="A258" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.ojousama.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postMatchWin.ojousama.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まだまだ楽しめそうですわね</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" ht="40" customHeight="1">
+      <c r="A259" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あら、決勝まで来ちゃいましたわ。楽しみですわね</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" ht="40" customHeight="1">
+      <c r="A260" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.ojousama.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.ojousama.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">最後の一戦！ 思いっきりやりますわよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="40" customHeight="1">
+      <c r="A261" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">さあ、楽しい時間の始まりですわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="262" ht="40" customHeight="1">
+      <c r="A262" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.ojousama.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.ojousama.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">気楽に参りましょう。でも負けませんわよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="263" ht="40" customHeight="1">
+      <c r="A263" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">summon.ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あら、わたくしも呼ばれましたの？ 面白そうですわね</t>
+        </is>
+      </c>
+    </row>
+    <row r="264" ht="40" customHeight="1">
+      <c r="A264" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.ojousama.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">summon.ojousama.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">わたくしが選ばれないわけがありませんわよね</t>
+        </is>
+      </c>
+    </row>
+    <row r="265" ht="40" customHeight="1">
+      <c r="A265" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">全力で参りますわ！ よろしくお願いいたしますの</t>
+        </is>
+      </c>
+    </row>
+    <row r="266" ht="40" customHeight="1">
+      <c r="A266" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まあ、勝っちゃいましたわ!最高の舞台で、最高の気分ですの!</t>
+        </is>
+      </c>
+    </row>
+    <row r="267" ht="40" customHeight="1">
+      <c r="A267" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あら〜、面白そうな団体ですわね。遊ばせていただきますわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="268" ht="40" customHeight="1">
+      <c r="A268" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.ojousama.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">ojousama.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">わたくしたちと勝負しません？ きっと楽しいですわよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="269" ht="40" customHeight="1">
+      <c r="A269" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あら〜、お断りですの？ もったいないですわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="270" ht="40" customHeight="1">
+      <c r="A270" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.ojousama.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">ojousama.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ま、いいですわ。またの機会にいたしましょう</t>
+        </is>
+      </c>
+    </row>
+    <row r="271" ht="40" customHeight="1">
+      <c r="A271" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_lose.ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あらあら、負けてしまいましたわ。でもくよくよしませんわ</t>
+        </is>
+      </c>
+    </row>
+    <row r="272" ht="40" customHeight="1">
+      <c r="A272" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.ojousama.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_lose.ojousama.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">次はもっと上手くやりますわよ〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="273" ht="40" customHeight="1">
+      <c r="A273" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">やりましたわ〜！ 勝利ですわ！</t>
+        </is>
+      </c>
+    </row>
+    <row r="274" ht="40" customHeight="1">
+      <c r="A274" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.ojousama.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.ojousama.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">楽しい対抗戦でしたわ。またぜひ</t>
+        </is>
+      </c>
+    </row>
+    <row r="275" ht="40" customHeight="1">
+      <c r="A275" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あら、勝ってしまいましたわ～。うちの団体、なかなかやりますでしょ？</t>
+        </is>
+      </c>
+    </row>
+    <row r="276" ht="40" customHeight="1">
+      <c r="A276" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">ojousama.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あらあら、勝っちゃいましたわね〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="277" ht="40" customHeight="1">
+      <c r="A277" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.easygoing[3]</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">ojousama.easygoing[3]</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">楽しかったですわ〜。またやりましょうね</t>
+        </is>
+      </c>
+    </row>
+    <row r="278" ht="40" customHeight="1">
+      <c r="A278" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">最後まで楽しゅうございましたわ。ありがとうございます</t>
+        </is>
+      </c>
+    </row>
+    <row r="279" ht="40" customHeight="1">
+      <c r="A279" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">巡り巡って、良い場所にご縁がありましたこと</t>
+        </is>
+      </c>
+    </row>
+    <row r="280" ht="40" customHeight="1">
+      <c r="A280" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">easygoing.ojousama[1]</t>
-        </is>
-      </c>
-      <c r="E241" t="inlineStr" s="2">
+      <c r="D280" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F241" t="inlineStr" s="3">
+      <c r="F280" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">うふふ♪見出されるって、とても気分がよいことですね</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H241"/>
+  <autoFilter ref="A1:H280"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/お嬢様×お気楽.xlsx
+++ b/セリフ編集/キャラタイプ別/お嬢様×お気楽.xlsx
@@ -262,7 +262,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H280"/>
+  <dimension ref="A1:H282"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -537,7 +537,7 @@
       </c>
       <c r="F8" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しかったですわ…でもここまでですわ！</t>
+          <t xml:space="preserve">楽しかったですわ…でもここまでですの！</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
       </c>
       <c r="F15" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">皆様の声援、しかと届きましたわ!最高の試合でしたの!</t>
+          <t xml:space="preserve">皆様の声援、しかと届きましたわ！最高の試合でしたの！</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
       </c>
       <c r="F17" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…負けてしまいましたわ、てへ</t>
+          <t xml:space="preserve">…負けてしまいましたわ…あらあら</t>
         </is>
       </c>
     </row>
@@ -889,7 +889,7 @@
       </c>
       <c r="F19" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、争奪戦ですの!?嬉しいですわ、頑張りますの!</t>
+          <t xml:space="preserve">まあ、争奪戦ですの！？嬉しいですわ、頑張りますの！</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="F20" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくお願いしますわ!楽しくやりましょうの!</t>
+          <t xml:space="preserve">よろしくお願いしますわ！楽しくやりましょう！</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       </c>
       <c r="F21" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">フリーも自由でよろしかったですけれど、こちらも楽しそうですわね!</t>
+          <t xml:space="preserve">フリーも自由でよろしかったですけれど、こちらも楽しそうですわね！</t>
         </is>
       </c>
     </row>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="F24" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">要らないと言われた者が勝ってしまいましたわ。よろしくて?</t>
+          <t xml:space="preserve">要らないと言われた者が勝ってしまいましたわ。よろしくて？</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F25" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしを切ったこと…少々、早まりましたわね?</t>
+          <t xml:space="preserve">わたくしを切ったこと…少々、早まりましたわね？</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2393,7 @@
       </c>
       <c r="F66" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ねえ社長、あの方と当ててくださいません?</t>
+          <t xml:space="preserve">ねえ社長、あの方と当ててくださいません？</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="F85" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、もう終わり? 少し物足りません。</t>
+          <t xml:space="preserve">あら、もう終わり？ 少し物足りません。</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="F100" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくし、こちらに残りますわ!ここ、とっても楽しいんですもの!</t>
+          <t xml:space="preserve">わたくし、こちらに残りますわ！ここ、とっても楽しいんですもの！</t>
         </is>
       </c>
     </row>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="F110" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いやはや社長。言いにくいのだけれど。{tenure}少し外の風に当たってみたくなって。</t>
+          <t xml:space="preserve">ごめんなさいね、社長。言いにくいのだけれど。{tenure}少し外の風に当たってみたくなって。</t>
         </is>
       </c>
     </row>
@@ -3961,7 +3961,7 @@
       </c>
       <c r="F115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長〜、わたくしたちのこと、たまには思い出してくださってもよろしくてよ?</t>
+          <t xml:space="preserve">社長〜、わたくしたちのこと、たまには思い出してくださってもよろしくてよ？</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="F116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長〜、次のメインカード、わたくしたちでいかがかしら?</t>
+          <t xml:space="preserve">社長〜、次のメインカード、わたくしたちでいかがかしら？</t>
         </is>
       </c>
     </row>
@@ -4025,7 +4025,7 @@
       </c>
       <c r="F117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長〜、お給金の件、少々考えてくださってもよろしくてよ?</t>
+          <t xml:space="preserve">社長〜、お給金の件、少々考えてくださってもよろしくてよ？</t>
         </is>
       </c>
     </row>
@@ -4057,7 +4057,7 @@
       </c>
       <c r="F118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長〜、わたくしたちの働き、たまには褒めてくださってもよろしくてよ?</t>
+          <t xml:space="preserve">社長〜、わたくしたちの働き、たまには褒めてくださってもよろしくてよ？</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="F121" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、別の形ですの? まあ、ありがたいですわ〜。</t>
+          <t xml:space="preserve">あら、別の形ですの？ まあ、ありがたいですわ〜。</t>
         </is>
       </c>
     </row>
@@ -4185,7 +4185,7 @@
       </c>
       <c r="F122" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ嬉しい、社長ありがとう! 華やかなメインにいたしますわ。</t>
+          <t xml:space="preserve">まあ嬉しい、社長ありがとう！ 華やかなメインにいたしますわ。</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
       </c>
       <c r="F124" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、そういう形ですの? まあ、ありがとうございますわ〜。</t>
+          <t xml:space="preserve">あら、そういう形ですの？ まあ、ありがとうございますわ〜。</t>
         </is>
       </c>
     </row>
@@ -4281,7 +4281,7 @@
       </c>
       <c r="F125" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ嬉しい! 社長ありがとうございますわ〜。</t>
+          <t xml:space="preserve">まあ嬉しい！ 社長ありがとうございますわ〜。</t>
         </is>
       </c>
     </row>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="F127" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、お金じゃない形ですの? まあ、それも素敵ですわね。</t>
+          <t xml:space="preserve">あら、お金じゃない形ですの？ まあ、それも素敵ですわね。</t>
         </is>
       </c>
     </row>
@@ -4377,7 +4377,7 @@
       </c>
       <c r="F128" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ嬉しい、社長に褒められちゃいましたわ〜!</t>
+          <t xml:space="preserve">まあ嬉しい、社長に褒められちゃいましたわ〜！</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="F130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、別の形ですの? まあ、ありがたいですわ〜。</t>
+          <t xml:space="preserve">あら、別の形ですの？ まあ、ありがたいですわ〜。</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="F131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、気にしてらしたの? 次はお誘いしますわ〜。</t>
+          <t xml:space="preserve">あら、気にしてらしたの？ 次はお誘いしますわ〜。</t>
         </is>
       </c>
     </row>
@@ -4601,7 +4601,7 @@
       </c>
       <c r="F135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、見られてましたの? では控えますわ〜。</t>
+          <t xml:space="preserve">あら、見られてましたの？ では控えますわ〜。</t>
         </is>
       </c>
     </row>
@@ -4665,7 +4665,7 @@
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、ばれてましたの? 明日から出ますわ〜。</t>
+          <t xml:space="preserve">あら、ばれてましたの？ 明日から出ますわ〜。</t>
         </is>
       </c>
     </row>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、見逃してくださるの? 助かりますわ〜。</t>
+          <t xml:space="preserve">まあ、見逃してくださるの？ 助かりますわ〜。</t>
         </is>
       </c>
     </row>
@@ -4729,7 +4729,7 @@
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、メンバー優先ですの? まあ、ありがたいですわ〜。</t>
+          <t xml:space="preserve">あら、メンバー優先ですの？ まあ、ありがたいですわ〜。</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、見ていてくださったの? ではお言葉に甘えますわ〜。</t>
+          <t xml:space="preserve">まあ、見ていてくださったの？ ではお言葉に甘えますわ〜。</t>
         </is>
       </c>
     </row>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、皆のケアですの? 助かりますわ〜。</t>
+          <t xml:space="preserve">あら、皆のケアですの？ 助かりますわ〜。</t>
         </is>
       </c>
     </row>
@@ -4857,7 +4857,7 @@
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、そんな話してましたの? 注意しておきますわ〜。</t>
+          <t xml:space="preserve">あら、そんな話してましたの？ 注意しておきますわ〜。</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、別ルートですの? 下の子のフォロー、お願いいたしますわ〜。</t>
+          <t xml:space="preserve">あら、別ルートですの？ 下の子のフォロー、お願いいたしますわ〜。</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、見られてましたの? 失礼いたしましたわ〜。</t>
+          <t xml:space="preserve">あら、見られてましたの？ 失礼いたしましたわ〜。</t>
         </is>
       </c>
     </row>
@@ -5017,7 +5017,7 @@
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、別の手立てですの? ありがたいですわ〜。</t>
+          <t xml:space="preserve">あら、別の手立てですの？ ありがたいですわ〜。</t>
         </is>
       </c>
     </row>
@@ -5049,7 +5049,7 @@
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、見ていらしたの? では緩めますわ〜。</t>
+          <t xml:space="preserve">あら、見ていらしたの？ では緩めますわ〜。</t>
         </is>
       </c>
     </row>
@@ -5081,7 +5081,7 @@
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、続けていいんですの? ありがとうございますわ〜。</t>
+          <t xml:space="preserve">まあ、続けていいんですの？ ありがとうございますわ〜。</t>
         </is>
       </c>
     </row>
@@ -5113,7 +5113,7 @@
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、わたくしより皆優先ですの? ありがたいですわ〜。</t>
+          <t xml:space="preserve">あら、わたくしより皆優先ですの？ ありがたいですわ〜。</t>
         </is>
       </c>
     </row>
@@ -5568,7 +5568,7 @@
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">autumnWarChampion.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
@@ -5593,14 +5593,14 @@
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の試合でしたわ！ お相手にも感謝ですの</t>
+          <t xml:space="preserve">まあ、頼もしい仲間ばかりで心強かったですわ。</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">bestMatch.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
@@ -5625,14 +5625,14 @@
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一年間お守りいたしましたわ。来年もこの座を守りますの</t>
+          <t xml:space="preserve">最高の試合でしたわ！ お相手にも感謝ですの</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">champion.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
@@ -5657,14 +5657,14 @@
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">殿堂入りですの…！ 夢のようですわ…</t>
+          <t xml:space="preserve">一年間お守りいたしましたわ。来年もこの座を守りますの</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5679,7 +5679,7 @@
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">hallOfFame.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
@@ -5689,14 +5689,14 @@
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVPですの！ 光栄ですわ。来年も精進いたしますの</t>
+          <t xml:space="preserve">殿堂入りですの…！ 夢のようですわ…</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">mvp.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
@@ -5721,14 +5721,14 @@
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ…！ 新人王ですの…！ 光栄ですわ</t>
+          <t xml:space="preserve">MVPですの！ 光栄ですわ。来年も精進いたしますの</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5738,12 +5738,12 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[1]</t>
+          <t xml:space="preserve">rookie.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
@@ -5753,14 +5753,14 @@
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、ドームですのね。なんだか楽しそうですわ</t>
+          <t xml:space="preserve">まあ…！ 新人王ですの…！ 光栄ですわ</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[2]</t>
+          <t xml:space="preserve">springTagChampion.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
@@ -5785,14 +5785,14 @@
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ気楽にいきますわよ、ほほほ</t>
+          <t xml:space="preserve">まあ、相棒と優勝なんて素敵な春になりましたわね。</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.easygoing[3]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5807,7 +5807,7 @@
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[3]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
@@ -5817,14 +5817,14 @@
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こういう大きな会場、わたくし嫌いじゃありませんの</t>
+          <t xml:space="preserve">あら、ドームですのね。なんだか楽しそうですわ</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5834,12 +5834,12 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[1]</t>
+          <t xml:space="preserve">ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
@@ -5849,14 +5849,14 @@
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ、満員ですのね! 嬉しゅうございますわ</t>
+          <t xml:space="preserve">まぁ気楽にいきますわよ、ほほほ</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.easygoing[3]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[2]</t>
+          <t xml:space="preserve">ojousama.easygoing[3]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -5881,14 +5881,14 @@
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなに楽しい日は、なかなかありませんの</t>
+          <t xml:space="preserve">こういう大きな会場、わたくし嫌いじゃありませんの</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.easygoing[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[3]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -5913,14 +5913,14 @@
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ほほほ、またやりたくなりますわ</t>
+          <t xml:space="preserve">まぁ、満員ですのね！ 嬉しゅうございますわ</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5930,29 +5930,29 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンの皆さまに、もっと近くで見ていただきたいんです</t>
+          <t xml:space="preserve">こんなに楽しい日は、なかなかありませんの</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.easygoing[3]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -5962,29 +5962,29 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">ojousama.easygoing[3]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">テレビ…！わたくし、出てみたいです</t>
+          <t xml:space="preserve">ほほほ、またやりたくなりますわ</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -5994,12 +5994,12 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.accept.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">E1.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
@@ -6009,14 +6009,14 @@
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、成功いたしましたの!わたくし、嬉しくて仕方ありませんわ!</t>
+          <t xml:space="preserve">ファンの皆さまに、もっと近くで見ていただきたいんです</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6026,29 +6026,29 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[1]</t>
+          <t xml:space="preserve">E1.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うふふ、ご一緒に楽しくやりましょうよ</t>
+          <t xml:space="preserve">テレビ…！わたくし、出てみたいです</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6058,29 +6058,29 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[2]</t>
+          <t xml:space="preserve">E1.accept.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">退屈なプロレスはしないと約束いたしますわ</t>
+          <t xml:space="preserve">まあ、成功いたしましたの！わたくし、嬉しくて仕方ありませんわ！</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6090,7 +6090,7 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
@@ -6105,14 +6105,14 @@
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、よろしくお願いしますわぁ</t>
+          <t xml:space="preserve">うふふ、ご一緒に楽しくやりましょうよ</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6122,7 +6122,7 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
@@ -6137,14 +6137,14 @@
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お仲間入りですわね。よろしくですの</t>
+          <t xml:space="preserve">退屈なプロレスはしないと約束いたしますわ</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
@@ -6169,14 +6169,14 @@
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ごきげんよう。新天地ですわ、暴れさせていただきますの</t>
+          <t xml:space="preserve">ふふ、よろしくお願いしますわぁ</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
@@ -6201,14 +6201,14 @@
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここなら好きにやれそうですわね。楽しみですの</t>
+          <t xml:space="preserve">お仲間入りですわね。よろしくですの</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
@@ -6233,14 +6233,14 @@
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、今日から仲間ですわね。よろしくお願いしますの</t>
+          <t xml:space="preserve">ごきげんよう。新天地ですわ、暴れさせていただきますの</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
@@ -6265,14 +6265,14 @@
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">皆様、楽しくやりましょうね</t>
+          <t xml:space="preserve">ここなら好きにやれそうですわね。楽しみですの</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
@@ -6297,14 +6297,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらあら…少し休みますわね</t>
+          <t xml:space="preserve">まあ、今日から仲間ですわね。よろしくお願いしますの</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6314,12 +6314,12 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6329,14 +6329,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うふふ、ご一緒に楽しくやりましょうよ</t>
+          <t xml:space="preserve">皆様、楽しくやりましょうね</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6346,12 +6346,12 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6361,14 +6361,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">退屈なプロレスはしないと約束いたしますわ</t>
+          <t xml:space="preserve">あらあら…少し休みますわね</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">draftInterest.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6393,14 +6393,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、よろしくお願いしますわぁ</t>
+          <t xml:space="preserve">うふふ、ご一緒に楽しくやりましょうよ</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">draftInterest.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6425,14 +6425,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お仲間入りですわね。よろしくですの</t>
+          <t xml:space="preserve">退屈なプロレスはしないと約束いたしますわ</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6447,7 +6447,7 @@
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">draftJoin.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6457,14 +6457,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">巡り巡って、良い場所にご縁がありましたこと</t>
+          <t xml:space="preserve">ふふ、よろしくお願いしますわぁ</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">draftJoin.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6489,14 +6489,14 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ごきげんよう。新天地ですわ、暴れさせていただきますの</t>
+          <t xml:space="preserve">お仲間入りですわね。よろしくですの</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">faGreeting.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6521,14 +6521,14 @@
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここなら好きにやれそうですわね。楽しみですの</t>
+          <t xml:space="preserve">巡り巡って、良い場所にご縁がありましたこと</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">faSigning.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6553,14 +6553,14 @@
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、今日から仲間ですわね。よろしくお願いしますの</t>
+          <t xml:space="preserve">ごきげんよう。新天地ですわ、暴れさせていただきますの</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6575,7 +6575,7 @@
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">faSigning.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6585,14 +6585,14 @@
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">皆様、楽しくやりましょうね</t>
+          <t xml:space="preserve">ここなら好きにやれそうですわね。楽しみですの</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">faWelcome.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6617,14 +6617,14 @@
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらあら…少し休みますわね</t>
+          <t xml:space="preserve">まあ、今日から仲間ですわね。よろしくお願いしますの</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">faWelcome.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6649,14 +6649,14 @@
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、こういうこともありますわね。ごきげんよう</t>
+          <t xml:space="preserve">皆様、楽しくやりましょうね</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6671,7 +6671,7 @@
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">injury.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6681,14 +6681,14 @@
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お邪魔いたしますわ。短い間ですけれど、暴れさせていただきますの</t>
+          <t xml:space="preserve">あらあら…少し休みますわね</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">release.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6713,14 +6713,14 @@
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一時のご縁ですもの、思い切りやらせていただきますわ</t>
+          <t xml:space="preserve">ふふ、こういうこともありますわね。ごきげんよう</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6735,7 +6735,7 @@
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">rentalGreeting.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6745,14 +6745,14 @@
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うふふ♪見出されるって、とても気分がよいことですね</t>
+          <t xml:space="preserve">お邪魔いたしますわ。短い間ですけれど、暴れさせていただきますの</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">rentalGreeting.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6777,14 +6777,14 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は負けてしまいましたけれど…次はもっとよい試合をしますわ</t>
+          <t xml:space="preserve">一時のご縁ですもの、思い切りやらせていただきますわ</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6799,7 +6799,7 @@
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">scoutGreeting.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6809,14 +6809,14 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいですけれど、俯いていては応援してくださる方に失礼ですもの</t>
+          <t xml:space="preserve">うふふ♪見出されるって、とても気分がよいことですね</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6841,14 +6841,14 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンはわたくしですの。また守り切りましたわ</t>
+          <t xml:space="preserve">今日は負けてしまいましたけれど…次はもっとよい試合をしますわ</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6863,7 +6863,7 @@
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">titleChallengeLoss.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6873,14 +6873,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よい試合でしたわ。またいつでも挑んでらして</t>
+          <t xml:space="preserve">悔しいですけれど、俯いていては応援してくださる方に失礼ですもの</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6895,7 +6895,7 @@
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">titleDefense.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6905,14 +6905,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けてしまいましたわ…でも応援してくださる方がいる限り、立ち上がりますの</t>
+          <t xml:space="preserve">チャンピオンはわたくしですの。また守り切りましたわ</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">titleDefense.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -6937,14 +6937,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ベルトのないわたくしなんて想像もできませんでしたわ。でも、わたくしはわたくしですもの</t>
+          <t xml:space="preserve">よい試合でしたわ。またいつでも挑んでらして</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6959,7 +6959,7 @@
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">titleLoss.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -6969,14 +6969,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">新チャンピオン誕生ですわ。ここからもっと盛り上げますの</t>
+          <t xml:space="preserve">負けてしまいましたわ…でも応援してくださる方がいる限り、立ち上がりますの</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">titleLoss.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7001,14 +7001,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルト、獲ってしまいましたわ。最高の気分ですの</t>
+          <t xml:space="preserve">…ベルトのないわたくしなんて想像もできませんでしたわ。でも、わたくしはわたくしですもの</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7018,12 +7018,12 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[1]</t>
+          <t xml:space="preserve">titleWin.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7033,14 +7033,14 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、こういうこともありますわね。ごきげんよう</t>
+          <t xml:space="preserve">新チャンピオン誕生ですわ。ここからもっと盛り上げますの</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[1]</t>
+          <t xml:space="preserve">titleWin.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7065,14 +7065,14 @@
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お邪魔いたしますわ。短い間ですけれど、暴れさせていただきますの</t>
+          <t xml:space="preserve">ベルト、獲ってしまいましたわ。最高の気分ですの</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[2]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7097,14 +7097,14 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一時のご縁ですもの、思い切りやらせていただきますわ</t>
+          <t xml:space="preserve">ふふ、こういうこともありますわね。ごきげんよう</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7114,7 +7114,7 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
@@ -7129,14 +7129,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は負けてしまいましたけれど…次はもっとよい試合をしますわ</t>
+          <t xml:space="preserve">お邪魔いたしますわ。短い間ですけれど、暴れさせていただきますの</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7146,7 +7146,7 @@
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="12">
@@ -7161,14 +7161,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいですけれど、俯いていては応援してくださる方に失礼ですもの</t>
+          <t xml:space="preserve">一時のご縁ですもの、思い切りやらせていただきますわ</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="12">
@@ -7193,14 +7193,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンはわたくしですの。また守り切りましたわ</t>
+          <t xml:space="preserve">今日は負けてしまいましたけれど…次はもっとよい試合をしますわ</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
@@ -7225,14 +7225,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よい試合でしたわ。またいつでも挑んでらして</t>
+          <t xml:space="preserve">悔しいですけれど、俯いていては応援してくださる方に失礼ですもの</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7242,7 +7242,7 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
@@ -7257,14 +7257,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けてしまいましたわ…でも応援してくださる方がいる限り、立ち上がりますの</t>
+          <t xml:space="preserve">チャンピオンはわたくしですの。また守り切りましたわ</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7274,7 +7274,7 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
@@ -7289,14 +7289,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ベルトのないわたくしなんて想像もできませんでしたわ。でも、わたくしはわたくしですもの</t>
+          <t xml:space="preserve">よい試合でしたわ。またいつでも挑んでらして</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7306,7 +7306,7 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
@@ -7321,14 +7321,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">新チャンピオン誕生ですわ。ここからもっと盛り上げますの</t>
+          <t xml:space="preserve">負けてしまいましたわ…でも応援してくださる方がいる限り、立ち上がりますの</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7338,7 +7338,7 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
@@ -7353,14 +7353,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルト、獲ってしまいましたわ。最高の気分ですの</t>
+          <t xml:space="preserve">…ベルトのないわたくしなんて想像もできませんでしたわ。でも、わたくしはわたくしですもの</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7370,29 +7370,29 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">う〜ん…少々、合いませんかしら…</t>
+          <t xml:space="preserve">新チャンピオン誕生ですわ。ここからもっと盛り上げますの</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7402,29 +7402,29 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、近ごろ少し素っ気ないような</t>
+          <t xml:space="preserve">ベルト、獲ってしまいましたわ。最高の気分ですの</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">bond_39_down.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7449,14 +7449,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">はて…空気が微かに変わりましたかしら</t>
+          <t xml:space="preserve">う〜ん…少々、合いませんかしら…</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7471,7 +7471,7 @@
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">bond_59_down.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7481,14 +7481,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しくお過ごしできますの〜</t>
+          <t xml:space="preserve">あら、近ごろ少し素っ気ないような</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">bond_59_down.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7513,14 +7513,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の相方。ずっとこのままでいたいものです</t>
+          <t xml:space="preserve">はて…空気が微かに変わりましたかしら</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7535,7 +7535,7 @@
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">bond_60_up.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7545,14 +7545,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒にいると、何もかも上手く回る気がして</t>
+          <t xml:space="preserve">楽しくお過ごしできますの〜</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7567,7 +7567,7 @@
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">bond_80_up.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7577,14 +7577,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">熱い間柄も一区切り。少し寂しいものです</t>
+          <t xml:space="preserve">最高の相方。ずっとこのままでいたいものです</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">bond_80_up.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7609,14 +7609,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ、因縁とて永遠ではありませんもの〜</t>
+          <t xml:space="preserve">一緒にいると、何もかも上手く回る気がして</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">rivalry_29_down.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7641,14 +7641,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">良い勝負になりそうです〜。少し燃えてきました</t>
+          <t xml:space="preserve">熱い間柄も一区切り。少し寂しいものです</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7663,7 +7663,7 @@
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">rivalry_29_down.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7673,14 +7673,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うふふ、負けたくありませんね</t>
+          <t xml:space="preserve">まぁ、因縁とて永遠ではありませんもの〜</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7695,7 +7695,7 @@
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">rivalry_30_up.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7705,14 +7705,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">本気でやり合いたい相手など、そういません</t>
+          <t xml:space="preserve">良い勝負になりそうです〜。少し燃えてきました</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">rivalry_30_up.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7737,14 +7737,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うふふ、思い浮かべるだけで力が入ります</t>
+          <t xml:space="preserve">うふふ、負けたくありませんね</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7759,7 +7759,7 @@
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">rivalry_50_up.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7769,14 +7769,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この試合が一番楽しい。ずっとこのままであればよいのに</t>
+          <t xml:space="preserve">本気でやり合いたい相手など、そういません</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7791,7 +7791,7 @@
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">rivalry_50_up.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7801,14 +7801,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">運命の好敵手…そう呼びたくなります</t>
+          <t xml:space="preserve">うふふ、思い浮かべるだけで力が入ります</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7823,7 +7823,7 @@
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">rivalry_70_up.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7833,14 +7833,14 @@
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここは素晴らしい〜。皆さんとやるのが楽しくて</t>
+          <t xml:space="preserve">この試合が一番楽しい。ずっとこのままであればよいのに</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7855,7 +7855,7 @@
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">rivalry_70_up.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -7865,14 +7865,14 @@
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体、とても居心地がよいのです〜</t>
+          <t xml:space="preserve">運命の好敵手…そう呼びたくなります</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">trust_above_75.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7897,14 +7897,14 @@
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">さすがにこれは…笑えません</t>
+          <t xml:space="preserve">ここは素晴らしい〜。皆さんとやるのが楽しくて</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7919,7 +7919,7 @@
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">trust_above_75.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7929,14 +7929,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うふふ…と笑っている場合ではありませんね、これは</t>
+          <t xml:space="preserve">この団体、とても居心地がよいのです〜</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">trust_below_20.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -7961,14 +7961,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">う〜ん…近ごろ少し胸がすっきりしません…</t>
+          <t xml:space="preserve">さすがにこれは…笑えません</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -7983,7 +7983,7 @@
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">trust_below_20.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -7993,14 +7993,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ大丈夫…ですよね？ 少し不安ですけれど</t>
+          <t xml:space="preserve">うふふ…と笑っている場合ではありませんね、これは</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8010,12 +8010,12 @@
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[1]</t>
+          <t xml:space="preserve">trust_below_35.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8025,14 +8025,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">連勝が止まりましたわ…でもまた頑張りますの</t>
+          <t xml:space="preserve">う〜ん…近ごろ少し胸がすっきりしません…</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8042,29 +8042,29 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">trust_below_35.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">傷だらけですけれど、最後まで来てしまいましたわ。ふふ、やるしかありませんわね</t>
+          <t xml:space="preserve">まぁ大丈夫…ですよね？ 少し不安ですけれど</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8074,29 +8074,29 @@
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">さすがに身体が重いですの。でも、締めくくりは楽しませていただきますわ</t>
+          <t xml:space="preserve">連勝が止まりましたわ…でもまた頑張りますの</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8111,7 +8111,7 @@
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">preFinal.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8121,14 +8121,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、お相手はどなた? 次から次へと、賑やかですこと</t>
+          <t xml:space="preserve">傷だらけですけれど、最後まで来てしまいましたわ。ふふ、やるしかありませんわね</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8143,7 +8143,7 @@
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">preFinal.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8153,14 +8153,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">賑やかな一日になりそうですわね。…面白いですわ</t>
+          <t xml:space="preserve">さすがに身体が重いですの。でも、締めくくりは楽しませていただきますわ</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8175,7 +8175,7 @@
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">preMatch.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8185,14 +8185,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、お見送りしましたわ。…ふぅ、まだ立っていますのよ。次はどなた?</t>
+          <t xml:space="preserve">あら、お相手はどなた？ 次から次へと、賑やかですこと</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8207,7 +8207,7 @@
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">preMatch.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8217,14 +8217,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、まだ終わりませんの? いいですわ、次の方、いらして</t>
+          <t xml:space="preserve">賑やかな一日になりそうですわね。…面白いですわ</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8234,12 +8234,12 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">survivor.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8249,14 +8249,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">素敵な三人でしたわ。この勝利は、お二人と分かち合いたいですの</t>
+          <t xml:space="preserve">一人、お見送りしましたわ。…ふぅ、まだ立っていますのよ。次はどなた？</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">survivor.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8281,14 +8281,14 @@
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お二人がいてくださったから、安心して戦えましたわ。ふふ</t>
+          <t xml:space="preserve">あら、まだ終わりませんの？ いいですわ、次の方、いらして</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8303,7 +8303,7 @@
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">champion.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8313,14 +8313,14 @@
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お賞はありがたいですわ。でも……お一人で笑うのは、趣味じゃありませんの</t>
+          <t xml:space="preserve">素敵な三人でしたわ。この勝利は、お二人と分かち合いたいですの</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8335,7 +8335,7 @@
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">champion.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8345,14 +8345,14 @@
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次はお三人で勝って、優雅に乾杯したいですわね</t>
+          <t xml:space="preserve">お二人がいてくださったから、安心して戦えましたわ。ふふ</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8367,7 +8367,7 @@
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">defiant.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8377,14 +8377,14 @@
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次から次へと来るのですもの。退屈しませんでしたわ。身体は少し重いですけれど</t>
+          <t xml:space="preserve">お賞はありがたいですわ。でも……お一人で笑うのは、趣味じゃありませんの</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8399,7 +8399,7 @@
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">defiant.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8409,14 +8409,14 @@
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人お相手したのかしら。まあ、全員お見送りしましたし、よろしいですわね</t>
+          <t xml:space="preserve">次はお三人で勝って、優雅に乾杯したいですわね</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="C255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">gauntlet.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8441,14 +8441,14 @@
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、優勝ですの！ 最高ですわ〜！</t>
+          <t xml:space="preserve">次から次へと来るのですもの。退屈しませんでしたわ。身体は少し重いですけれど</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">gauntlet.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8473,14 +8473,14 @@
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やりましたわ〜！ ご褒美が楽しみですわね</t>
+          <t xml:space="preserve">何人お相手したのかしら。まあ、全員お見送りしましたし、よろしいですわね</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8495,7 +8495,7 @@
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">champion.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8505,14 +8505,14 @@
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やりましたわ。この調子で行きますわよ</t>
+          <t xml:space="preserve">あらあら、優勝ですって。うまくいくものですわね</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8527,7 +8527,7 @@
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">champion.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8537,14 +8537,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだまだ楽しめそうですわね</t>
+          <t xml:space="preserve">やりましたわ〜！ ご褒美が楽しみですわね</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8559,7 +8559,7 @@
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">postMatchWin.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8569,14 +8569,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、決勝まで来ちゃいましたわ。楽しみですわね</t>
+          <t xml:space="preserve">やりましたわ。この調子で行きますわよ</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">postMatchWin.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8601,14 +8601,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最後の一戦！ 思いっきりやりますわよ</t>
+          <t xml:space="preserve">まだまだ楽しめそうですわね</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8623,7 +8623,7 @@
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">preFinal.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8633,14 +8633,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">さあ、楽しい時間の始まりですわ</t>
+          <t xml:space="preserve">あら、決勝まで来ちゃいましたわ。楽しみですわね</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8655,7 +8655,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">preFinal.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8665,14 +8665,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">気楽に参りましょう。でも負けませんわよ</t>
+          <t xml:space="preserve">最後の一戦！ 思いっきりやりますわよ</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8687,7 +8687,7 @@
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">preMatch.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8697,14 +8697,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、わたくしも呼ばれましたの？ 面白そうですわね</t>
+          <t xml:space="preserve">さあ、楽しい時間の始まりですわ</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8719,7 +8719,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">preMatch.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8729,14 +8729,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしが選ばれないわけがありませんわよね</t>
+          <t xml:space="preserve">気楽に参りましょう。でも負けませんわよ</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="C265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[1]</t>
+          <t xml:space="preserve">summon.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8761,14 +8761,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力で参りますわ！ よろしくお願いいたしますの</t>
+          <t xml:space="preserve">あら、わたくしも呼ばれましたの？ 面白そうですわね</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8778,12 +8778,12 @@
       </c>
       <c r="C266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[1]</t>
+          <t xml:space="preserve">summon.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8793,14 +8793,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、勝っちゃいましたわ!最高の舞台で、最高の気分ですの!</t>
+          <t xml:space="preserve">あらあら、お声がかかってしまって。断る理由もありませんわね</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8810,7 +8810,7 @@
       </c>
       <c r="C267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D267" t="inlineStr" s="12">
@@ -8825,14 +8825,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら〜、面白そうな団体ですわね。遊ばせていただきますわ</t>
+          <t xml:space="preserve">全力で参りますわ！ よろしくお願いいたしますの</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[2]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -8857,14 +8857,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしたちと勝負しません？ きっと楽しいですわよ</t>
+          <t xml:space="preserve">まあ、勝っちゃいましたわ！最高の舞台で、最高の気分ですの！</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="C269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D269" t="inlineStr" s="12">
@@ -8889,14 +8889,14 @@
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら〜、お断りですの？ もったいないですわ</t>
+          <t xml:space="preserve">あら〜、面白そうな団体ですわね。遊ばせていただきますわ</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="C270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D270" t="inlineStr" s="12">
@@ -8921,14 +8921,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、いいですわ。またの機会にいたしましょう</t>
+          <t xml:space="preserve">わたくしたちと勝負しません？ きっと楽しいですわよ</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="C271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -8953,14 +8953,14 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらあら、負けてしまいましたわ。でもくよくよしませんわ</t>
+          <t xml:space="preserve">あら〜、お断りですの？ もったいないですわ</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -8985,14 +8985,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次はもっと上手くやりますわよ〜</t>
+          <t xml:space="preserve">ま、いいですわ。またの機会にいたしましょう</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9007,7 +9007,7 @@
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">result_lose.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9017,14 +9017,14 @@
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やりましたわ〜！ 勝利ですわ！</t>
+          <t xml:space="preserve">あらあら、負けてしまいましたわ。でもくよくよしませんわ</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">result_lose.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9049,14 +9049,14 @@
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しい対抗戦でしたわ。またぜひ</t>
+          <t xml:space="preserve">次はもっと上手くやりますわよ〜</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="C275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[1]</t>
+          <t xml:space="preserve">result_win.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9081,14 +9081,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、勝ってしまいましたわ～。うちの団体、なかなかやりますでしょ？</t>
+          <t xml:space="preserve">あらあら、勝ってしまいましたわね</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9098,12 +9098,12 @@
       </c>
       <c r="C276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[2]</t>
+          <t xml:space="preserve">result_win.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9113,14 +9113,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらあら、勝っちゃいましたわね〜</t>
+          <t xml:space="preserve">楽しい対抗戦でしたわ。またぜひ</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.easygoing[3]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9135,7 +9135,7 @@
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[3]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9145,14 +9145,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しかったですわ〜。またやりましょうね</t>
+          <t xml:space="preserve">あら、勝ってしまいましたわ〜。うちの団体、なかなかやりますでしょ？</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9162,29 +9162,29 @@
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最後まで楽しゅうございましたわ。ありがとうございます</t>
+          <t xml:space="preserve">あらあら、勝っちゃいましたわね〜</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.easygoing[3]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9194,59 +9194,123 @@
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[1]</t>
+          <t xml:space="preserve">ojousama.easygoing[3]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">巡り巡って、良い場所にご縁がありましたこと</t>
+          <t xml:space="preserve">楽しかったですわ〜。またやりましょうね</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">最後まで楽しゅうございましたわ。ありがとうございます</t>
+        </is>
+      </c>
+    </row>
+    <row r="281" ht="40" customHeight="1">
+      <c r="A281" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">巡り巡って、良い場所にご縁がありましたこと</t>
+        </is>
+      </c>
+    </row>
+    <row r="282" ht="40" customHeight="1">
+      <c r="A282" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
-      <c r="B280" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr" s="2">
+      <c r="B282" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr" s="12">
+      <c r="D282" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
-      <c r="E280" t="inlineStr" s="2">
+      <c r="E282" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F280" t="inlineStr" s="3">
+      <c r="F282" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">うふふ♪見出されるって、とても気分がよいことですね</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H280"/>
+  <autoFilter ref="A1:H282"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/お嬢様×お気楽.xlsx
+++ b/セリフ編集/キャラタイプ別/お嬢様×お気楽.xlsx
@@ -262,7 +262,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H282"/>
+  <dimension ref="A1:H289"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -3488,7 +3488,7 @@
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_accept.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">decline_accept.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="2">
@@ -3513,14 +3513,14 @@
       </c>
       <c r="F101" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、うれしい！ さすが社長ですこと。今年も楽しくまいりましょうね。</t>
+          <t xml:space="preserve">ええ、それでよろしいのよ。……お気になさらないで。お茶でも、いかが？</t>
         </is>
       </c>
     </row>
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_hold.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">decline_hold.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr" s="2">
@@ -3545,14 +3545,14 @@
       </c>
       <c r="F102" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、まあ良いことにいたしましょう。いただけるだけ幸運ですもの。</t>
+          <t xml:space="preserve">あらあら、そんなことをなさって。……ふふ、責任は取ってさしあげますわね</t>
         </is>
       </c>
     </row>
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_open.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">decline_open.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr" s="2">
@@ -3577,14 +3577,14 @@
       </c>
       <c r="F103" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらら、だめですのね。まあ仕方ありません。……少し、しょげてしまいます。</t>
+          <t xml:space="preserve">あらあら、そういうお話。……ええ、ちゃんと伺いますから、どうぞ</t>
         </is>
       </c>
     </row>
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_strict.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">decline_strict.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="2">
@@ -3609,14 +3609,14 @@
       </c>
       <c r="F104" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございますわ。前向きに検討いたしますの</t>
+          <t xml:space="preserve">まあ。……そこまできっちり数えられると、笑うしかありませんわね</t>
         </is>
       </c>
     </row>
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_accept.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">decline_voluntary_accept.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
@@ -3641,14 +3641,14 @@
       </c>
       <c r="F105" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、やはりだめですのね。まあ仕方ありません。でも、いつか上げてくださいませ。約束ですわよ。</t>
+          <t xml:space="preserve">素直に下げてくださるのね。……そういう方、嫌いではなくてよ</t>
         </is>
       </c>
     </row>
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_hold.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">decline_voluntary_hold.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="2">
@@ -3673,14 +3673,14 @@
       </c>
       <c r="F106" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、とうとうこの日が参りましたのね。では、お元気で。</t>
+          <t xml:space="preserve">あらあら、聞いてくださらないのね。……ふふ、では甘えてしまいましょうか</t>
         </is>
       </c>
     </row>
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_open.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3695,7 +3695,7 @@
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">decline_voluntary_open.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
@@ -3705,14 +3705,14 @@
       </c>
       <c r="F107" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">そろそろ潮時かしら。楽しゅうございました、ええ。ごきげんよう。</t>
+          <t xml:space="preserve">社長、そろそろお値下げの頃合いではなくて？ ……お互い、目は確かでしょう</t>
         </is>
       </c>
     </row>
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">raise_accept.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="2">
@@ -3737,14 +3737,14 @@
       </c>
       <c r="F108" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">聞いてくださるの？ そうねえ……{record}なんだか、代わり映えしなくて。新しいことがしてみたいの。</t>
+          <t xml:space="preserve">まあ、うれしい！ さすが社長ですこと。今年も楽しくまいりましょうね。</t>
         </is>
       </c>
     </row>
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="2">
@@ -3769,14 +3769,14 @@
       </c>
       <c r="F109" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、あのね。{tenure}いろいろ考えたのだけれど……環境を変えてみようかしら、と。</t>
+          <t xml:space="preserve">ふふ、まあ良いことにいたしましょう。いただけるだけ幸運ですもの。</t>
         </is>
       </c>
     </row>
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="2">
@@ -3801,14 +3801,14 @@
       </c>
       <c r="F110" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ごめんなさいね、社長。言いにくいのだけれど。{tenure}少し外の風に当たってみたくなって。</t>
+          <t xml:space="preserve">あらら、だめですのね。まあ仕方ありません。……少し、しょげてしまいます。</t>
         </is>
       </c>
     </row>
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">raise_open.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
@@ -3833,14 +3833,14 @@
       </c>
       <c r="F111" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、まあそうなりますわよね。{tenure_farewell}{rivalry}どうか、お元気で。</t>
+          <t xml:space="preserve">ありがとうございますわ。前向きに検討いたしますの</t>
         </is>
       </c>
     </row>
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">raise_refuse.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
@@ -3865,14 +3865,14 @@
       </c>
       <c r="F112" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ごめんなさい社長……。お金の話ではないの。もう、心が決まってしまったから。</t>
+          <t xml:space="preserve">ふふ、やはりだめですのね。まあ仕方ありません。でも、いつか上げてくださいませ。約束ですわよ。</t>
         </is>
       </c>
     </row>
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">sudden_departure.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
@@ -3897,14 +3897,14 @@
       </c>
       <c r="F113" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、そこまでしてくださるの？ ……では、もう少しだけ居させていただこうかしら。</t>
+          <t xml:space="preserve">まあ、とうとうこの日が参りましたのね。では、お元気で。</t>
         </is>
       </c>
     </row>
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3914,12 +3914,12 @@
       </c>
       <c r="C114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">start.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">sudden_departure.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -3929,14 +3929,14 @@
       </c>
       <c r="F114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">条件をお聞かせくださいまし。それ次第ですわ</t>
+          <t xml:space="preserve">そろそろ潮時かしら。楽しゅうございました、ええ。ごきげんよう。</t>
         </is>
       </c>
     </row>
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -3946,29 +3946,29 @@
       </c>
       <c r="C115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">transfer_listen.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長〜、わたくしたちのこと、たまには思い出してくださってもよろしくてよ？</t>
+          <t xml:space="preserve">聞いてくださるの？ そうねえ……{record}なんだか、代わり映えしなくて。新しいことがしてみたいの。</t>
         </is>
       </c>
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -3978,29 +3978,29 @@
       </c>
       <c r="C116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">transfer_open.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長〜、次のメインカード、わたくしたちでいかがかしら？</t>
+          <t xml:space="preserve">社長、あのね。{tenure}いろいろ考えたのだけれど……環境を変えてみようかしら、と。</t>
         </is>
       </c>
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4010,29 +4010,29 @@
       </c>
       <c r="C117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">transfer_open.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長〜、お給金の件、少々考えてくださってもよろしくてよ？</t>
+          <t xml:space="preserve">ごめんなさいね、社長。言いにくいのだけれど。{tenure}少し外の風に当たってみたくなって。</t>
         </is>
       </c>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4042,29 +4042,29 @@
       </c>
       <c r="C118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">transfer_release.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長〜、わたくしたちの働き、たまには褒めてくださってもよろしくてよ？</t>
+          <t xml:space="preserve">ふふ、まあそうなりますわよね。{tenure_farewell}{rivalry}どうか、お元気で。</t>
         </is>
       </c>
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4074,29 +4074,29 @@
       </c>
       <c r="C119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">transfer_retain_fail.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ嬉しい、社長ありがとうございますわ〜。</t>
+          <t xml:space="preserve">ごめんなさい社長……。お金の話ではないの。もう、心が決まってしまったから。</t>
         </is>
       </c>
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4106,29 +4106,29 @@
       </c>
       <c r="C120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">transfer_retain_success.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、そうですの。お時間取らせてしまいましたわね〜。</t>
+          <t xml:space="preserve">あら、そこまでしてくださるの？ ……では、もう少しだけ居させていただこうかしら。</t>
         </is>
       </c>
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4138,29 +4138,29 @@
       </c>
       <c r="C121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">start.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F121" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、別の形ですの？ まあ、ありがたいですわ〜。</t>
+          <t xml:space="preserve">条件をお聞かせくださいまし。それ次第ですわ</t>
         </is>
       </c>
     </row>
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4175,7 +4175,7 @@
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
@@ -4185,14 +4185,14 @@
       </c>
       <c r="F122" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ嬉しい、社長ありがとう！ 華やかなメインにいたしますわ。</t>
+          <t xml:space="preserve">社長〜、わたくしたちのこと、たまには思い出してくださってもよろしくてよ？</t>
         </is>
       </c>
     </row>
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
@@ -4217,14 +4217,14 @@
       </c>
       <c r="F123" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、つれないですこと。次は期待してますわ〜。</t>
+          <t xml:space="preserve">社長〜、次のメインカード、わたくしたちでいかがかしら？</t>
         </is>
       </c>
     </row>
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
@@ -4249,14 +4249,14 @@
       </c>
       <c r="F124" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、そういう形ですの？ まあ、ありがとうございますわ〜。</t>
+          <t xml:space="preserve">社長〜、お給金の件、少々考えてくださってもよろしくてよ？</t>
         </is>
       </c>
     </row>
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
@@ -4281,14 +4281,14 @@
       </c>
       <c r="F125" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ嬉しい！ 社長ありがとうございますわ〜。</t>
+          <t xml:space="preserve">社長〜、わたくしたちの働き、たまには褒めてくださってもよろしくてよ？</t>
         </is>
       </c>
     </row>
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr" s="2">
@@ -4313,14 +4313,14 @@
       </c>
       <c r="F126" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、そうですの。まあ仕方ありませんわ〜。</t>
+          <t xml:space="preserve">まあ嬉しい、社長ありがとうございますわ〜。</t>
         </is>
       </c>
     </row>
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr" s="2">
@@ -4345,14 +4345,14 @@
       </c>
       <c r="F127" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、お金じゃない形ですの？ まあ、それも素敵ですわね。</t>
+          <t xml:space="preserve">あら、そうですの。お時間取らせてしまいましたわね〜。</t>
         </is>
       </c>
     </row>
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="2">
@@ -4377,14 +4377,14 @@
       </c>
       <c r="F128" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ嬉しい、社長に褒められちゃいましたわ〜！</t>
+          <t xml:space="preserve">あら、別の形ですの？ まあ、ありがたいですわ〜。</t>
         </is>
       </c>
     </row>
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4399,7 +4399,7 @@
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr" s="2">
@@ -4409,14 +4409,14 @@
       </c>
       <c r="F129" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、つれないですこと。まあいいですわ〜。</t>
+          <t xml:space="preserve">まあ嬉しい、社長ありがとう！ 華やかなメインにいたしますわ。</t>
         </is>
       </c>
     </row>
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr" s="2">
@@ -4441,14 +4441,14 @@
       </c>
       <c r="F130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、別の形ですの？ まあ、ありがたいですわ〜。</t>
+          <t xml:space="preserve">まあ、つれないですこと。次は期待してますわ〜。</t>
         </is>
       </c>
     </row>
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr" s="2">
@@ -4473,14 +4473,14 @@
       </c>
       <c r="F131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、気にしてらしたの？ 次はお誘いしますわ〜。</t>
+          <t xml:space="preserve">あら、そういう形ですの？ まあ、ありがとうございますわ〜。</t>
         </is>
       </c>
     </row>
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4495,7 +4495,7 @@
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
@@ -4505,14 +4505,14 @@
       </c>
       <c r="F132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございますわ〜、楽しんで参りますわ。</t>
+          <t xml:space="preserve">まあ嬉しい！ 社長ありがとうございますわ〜。</t>
         </is>
       </c>
     </row>
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
@@ -4537,14 +4537,14 @@
       </c>
       <c r="F133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、配慮が足りませんでしたわね〜。気をつけますわ。</t>
+          <t xml:space="preserve">あら、そうですの。まあ仕方ありませんわ〜。</t>
         </is>
       </c>
     </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
@@ -4569,14 +4569,14 @@
       </c>
       <c r="F134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございますわ〜。</t>
+          <t xml:space="preserve">あら、お金じゃない形ですの？ まあ、それも素敵ですわね。</t>
         </is>
       </c>
     </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
@@ -4601,14 +4601,14 @@
       </c>
       <c r="F135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、見られてましたの？ では控えますわ〜。</t>
+          <t xml:space="preserve">まあ嬉しい、社長に褒められちゃいましたわ〜！</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4623,7 +4623,7 @@
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
@@ -4633,14 +4633,14 @@
       </c>
       <c r="F136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、ご理解ありがとうございますわ〜。続けますわよ。</t>
+          <t xml:space="preserve">あら、つれないですこと。まあいいですわ〜。</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
@@ -4665,14 +4665,14 @@
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、ばれてましたの？ 明日から出ますわ〜。</t>
+          <t xml:space="preserve">あら、別の形ですの？ まあ、ありがたいですわ〜。</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
@@ -4697,14 +4697,14 @@
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、見逃してくださるの？ 助かりますわ〜。</t>
+          <t xml:space="preserve">あら、気にしてらしたの？ 次はお誘いしますわ〜。</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
@@ -4729,14 +4729,14 @@
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、メンバー優先ですの？ まあ、ありがたいですわ〜。</t>
+          <t xml:space="preserve">ありがとうございますわ〜、楽しんで参りますわ。</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4751,7 +4751,7 @@
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
@@ -4761,14 +4761,14 @@
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、見ていてくださったの？ ではお言葉に甘えますわ〜。</t>
+          <t xml:space="preserve">あら、配慮が足りませんでしたわね〜。気をつけますわ。</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
@@ -4793,14 +4793,14 @@
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、まだ大丈夫ですのよ〜。</t>
+          <t xml:space="preserve">ありがとうございますわ〜。</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
@@ -4825,14 +4825,14 @@
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、皆のケアですの？ 助かりますわ〜。</t>
+          <t xml:space="preserve">あら、見られてましたの？ では控えますわ〜。</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4847,7 +4847,7 @@
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
@@ -4857,14 +4857,14 @@
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、そんな話してましたの？ 注意しておきますわ〜。</t>
+          <t xml:space="preserve">まあ、ご理解ありがとうございますわ〜。続けますわよ。</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
@@ -4889,14 +4889,14 @@
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございますわ〜。穏便に、ですわね。</t>
+          <t xml:space="preserve">あら、ばれてましたの？ 明日から出ますわ〜。</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
@@ -4921,14 +4921,14 @@
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、別ルートですの？ 下の子のフォロー、お願いいたしますわ〜。</t>
+          <t xml:space="preserve">まあ、見逃してくださるの？ 助かりますわ〜。</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
@@ -4953,14 +4953,14 @@
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、見られてましたの？ 失礼いたしましたわ〜。</t>
+          <t xml:space="preserve">あら、メンバー優先ですの？ まあ、ありがたいですわ〜。</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -4975,7 +4975,7 @@
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
@@ -4985,14 +4985,14 @@
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（あら、と微笑んで、お話を流しましたわ）</t>
+          <t xml:space="preserve">まあ、見ていてくださったの？ ではお言葉に甘えますわ〜。</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
@@ -5017,14 +5017,14 @@
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、別の手立てですの？ ありがたいですわ〜。</t>
+          <t xml:space="preserve">まあ、まだ大丈夫ですのよ〜。</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5039,7 +5039,7 @@
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
@@ -5049,14 +5049,14 @@
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、見ていらしたの？ では緩めますわ〜。</t>
+          <t xml:space="preserve">あら、皆のケアですの？ 助かりますわ〜。</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
@@ -5081,14 +5081,14 @@
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、続けていいんですの？ ありがとうございますわ〜。</t>
+          <t xml:space="preserve">あら、そんな話してましたの？ 注意しておきますわ〜。</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
@@ -5113,14 +5113,14 @@
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、わたくしより皆優先ですの？ ありがたいですわ〜。</t>
+          <t xml:space="preserve">ありがとうございますわ〜。穏便に、ですわね。</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.easygoing.attack.ojousama</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="C152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.attack.ojousama</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
@@ -5145,14 +5145,14 @@
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲良しごっこは、もう終わりですわね</t>
+          <t xml:space="preserve">あら、別ルートですの？ 下の子のフォロー、お願いいたしますわ〜。</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.easygoing.defend.ojousama</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5162,12 +5162,12 @@
       </c>
       <c r="C153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.defend.ojousama</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
@@ -5177,29 +5177,29 @@
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、仕方ありませんわね</t>
+          <t xml:space="preserve">あら、見られてましたの？ 失礼いたしましたわ〜。</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
@@ -5209,14 +5209,14 @@
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、そんな昔のこと、もう忘れていますわよ。</t>
+          <t xml:space="preserve">（あら、と微笑んで、お話を流しましたわ）</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5226,29 +5226,29 @@
       </c>
       <c r="C155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近絶好調ですわ！ もっと上に行けそうですの</t>
+          <t xml:space="preserve">あら、別の手立てですの？ ありがたいですわ〜。</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5258,29 +5258,29 @@
       </c>
       <c r="C156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、もうこれ以上は？ まあ、十分ですわ</t>
+          <t xml:space="preserve">あら、見ていらしたの？ では緩めますわ〜。</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5290,29 +5290,29 @@
       </c>
       <c r="C157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来れるとは思いませんでしたわ！</t>
+          <t xml:space="preserve">まあ、続けていいんですの？ ありがとうございますわ〜。</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5322,29 +5322,29 @@
       </c>
       <c r="C158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">順調に成長してますわ♪</t>
+          <t xml:space="preserve">あら、わたくしより皆優先ですの？ ありがたいですわ〜。</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.easygoing.attack.ojousama</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5354,29 +5354,29 @@
       </c>
       <c r="C159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">easygoing.attack.ojousama</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらまあ…とんでもないところまで来てしまいましたわ</t>
+          <t xml:space="preserve">仲良しごっこは、もう終わりですわね</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.easygoing.defend.ojousama</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5386,61 +5386,61 @@
       </c>
       <c r="C160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_growth.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">easygoing.defend.ojousama</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンの方が増えて嬉しいですわ！</t>
+          <t xml:space="preserve">まあ、仕方ありませんわね</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
       <c r="C161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES</t>
         </is>
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、こんなに！ もっともっと楽しんでまいりましょう！</t>
+          <t xml:space="preserve">あら、そんな昔のこと、もう忘れていますわよ。</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="12">
@@ -5465,14 +5465,14 @@
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">少しやる気が出ませんの…でも頑張りますわ</t>
+          <t xml:space="preserve">最近絶好調ですわ！ もっと上に行けそうですの</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[1]</t>
+          <t xml:space="preserve">cap_reached.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
@@ -5497,14 +5497,14 @@
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やる気が戻ってまいりましたわ！ もう大丈夫ですの</t>
+          <t xml:space="preserve">あら、もうこれ以上は？ まあ、十分ですわ</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5514,12 +5514,12 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[1]</t>
+          <t xml:space="preserve">ovr_elite.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
@@ -5529,14 +5529,14 @@
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">調子が戻ってまいりましたわ！ もう大丈夫ですの</t>
+          <t xml:space="preserve">ここまで来れるとは思いませんでしたわ！</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5546,12 +5546,12 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">ovr_growth.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
@@ -5561,14 +5561,14 @@
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近少し不調ですの…でもすぐ立て直しますわ</t>
+          <t xml:space="preserve">順調に成長してますわ♪</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5578,29 +5578,29 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">autumnWarChampion.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">ovr_legend.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、頼もしい仲間ばかりで心強かったですわ。</t>
+          <t xml:space="preserve">あらまあ…とんでもないところまで来てしまいましたわ</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5610,29 +5610,29 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">pop_growth.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の試合でしたわ！ お相手にも感謝ですの</t>
+          <t xml:space="preserve">ファンの方が増えて嬉しいですわ！</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5642,29 +5642,29 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">pop_star.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一年間お守りいたしましたわ。来年もこの座を守りますの</t>
+          <t xml:space="preserve">まあ、こんなに！ もっともっと楽しんでまいりましょう！</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5674,29 +5674,29 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">殿堂入りですの…！ 夢のようですわ…</t>
+          <t xml:space="preserve">少しやる気が出ませんの…でも頑張りますわ</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5706,29 +5706,29 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVPですの！ 光栄ですわ。来年も精進いたしますの</t>
+          <t xml:space="preserve">やる気が戻ってまいりましたわ！ もう大丈夫ですの</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5738,29 +5738,29 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ…！ 新人王ですの…！ 光栄ですわ</t>
+          <t xml:space="preserve">調子が戻ってまいりましたわ！ もう大丈夫ですの</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.springTagChampion.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5770,29 +5770,29 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">springTagChampion.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">defeat.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、相棒と優勝なんて素敵な春になりましたわね。</t>
+          <t xml:space="preserve">最近少し不調ですの…でもすぐ立て直しますわ</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[1]</t>
+          <t xml:space="preserve">autumnWarChampion.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
@@ -5817,14 +5817,14 @@
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、ドームですのね。なんだか楽しそうですわ</t>
+          <t xml:space="preserve">まあ、頼もしい仲間ばかりで心強かったですわ。</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5834,12 +5834,12 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[2]</t>
+          <t xml:space="preserve">bestMatch.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
@@ -5849,14 +5849,14 @@
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ気楽にいきますわよ、ほほほ</t>
+          <t xml:space="preserve">最高の試合でしたわ！ お相手にも感謝ですの</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.easygoing[3]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[3]</t>
+          <t xml:space="preserve">champion.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -5881,14 +5881,14 @@
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こういう大きな会場、わたくし嫌いじゃありませんの</t>
+          <t xml:space="preserve">一年間お守りいたしましたわ。来年もこの座を守りますの</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[1]</t>
+          <t xml:space="preserve">hallOfFame.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -5913,14 +5913,14 @@
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ、満員ですのね！ 嬉しゅうございますわ</t>
+          <t xml:space="preserve">殿堂入りですの…！ 夢のようですわ…</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[2]</t>
+          <t xml:space="preserve">mvp.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -5945,14 +5945,14 @@
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなに楽しい日は、なかなかありませんの</t>
+          <t xml:space="preserve">MVPですの！ 光栄ですわ。来年も精進いたしますの</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.easygoing[3]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -5962,12 +5962,12 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[3]</t>
+          <t xml:space="preserve">rookie.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -5977,14 +5977,14 @@
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ほほほ、またやりたくなりますわ</t>
+          <t xml:space="preserve">まあ…！ 新人王ですの…！ 光栄ですわ</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -5994,29 +5994,29 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">springTagChampion.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンの皆さまに、もっと近くで見ていただきたいんです</t>
+          <t xml:space="preserve">まあ、相棒と優勝なんて素敵な春になりましたわね。</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6026,29 +6026,29 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">テレビ…！わたくし、出てみたいです</t>
+          <t xml:space="preserve">あら、ドームですのね。なんだか楽しそうですわ</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6058,29 +6058,29 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.accept.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、成功いたしましたの！わたくし、嬉しくて仕方ありませんわ！</t>
+          <t xml:space="preserve">まぁ気楽にいきますわよ、ほほほ</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.ojousama.easygoing[3]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6090,29 +6090,29 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[1]</t>
+          <t xml:space="preserve">ojousama.easygoing[3]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うふふ、ご一緒に楽しくやりましょうよ</t>
+          <t xml:space="preserve">こういう大きな会場、わたくし嫌いじゃありませんの</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6122,29 +6122,29 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[2]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">退屈なプロレスはしないと約束いたしますわ</t>
+          <t xml:space="preserve">まぁ、満員ですのね！ 嬉しゅうございますわ</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6154,29 +6154,29 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[1]</t>
+          <t xml:space="preserve">ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、よろしくお願いしますわぁ</t>
+          <t xml:space="preserve">こんなに楽しい日は、なかなかありませんの</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.ojousama.easygoing[3]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6186,29 +6186,29 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[2]</t>
+          <t xml:space="preserve">ojousama.easygoing[3]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お仲間入りですわね。よろしくですの</t>
+          <t xml:space="preserve">ほほほ、またやりたくなりますわ</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6218,29 +6218,29 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[1]</t>
+          <t xml:space="preserve">E1.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ごきげんよう。新天地ですわ、暴れさせていただきますの</t>
+          <t xml:space="preserve">ファンの皆さまに、もっと近くで見ていただきたいんです</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6250,29 +6250,29 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[2]</t>
+          <t xml:space="preserve">E1.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここなら好きにやれそうですわね。楽しみですの</t>
+          <t xml:space="preserve">テレビ…！わたくし、出てみたいです</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6282,29 +6282,29 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[1]</t>
+          <t xml:space="preserve">E1.accept.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、今日から仲間ですわね。よろしくお願いしますの</t>
+          <t xml:space="preserve">まあ、成功いたしましたの！わたくし、嬉しくて仕方ありませんわ！</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6314,12 +6314,12 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[2]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6329,14 +6329,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">皆様、楽しくやりましょうね</t>
+          <t xml:space="preserve">うふふ、ご一緒に楽しくやりましょうよ</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6346,12 +6346,12 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[1]</t>
+          <t xml:space="preserve">ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6361,14 +6361,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらあら…少し休みますわね</t>
+          <t xml:space="preserve">退屈なプロレスはしないと約束いたしますわ</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6378,12 +6378,12 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6393,14 +6393,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うふふ、ご一緒に楽しくやりましょうよ</t>
+          <t xml:space="preserve">ふふ、よろしくお願いしますわぁ</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6425,14 +6425,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">退屈なプロレスはしないと約束いたしますわ</t>
+          <t xml:space="preserve">お仲間入りですわね。よろしくですの</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6442,12 +6442,12 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6457,14 +6457,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、よろしくお願いしますわぁ</t>
+          <t xml:space="preserve">ごきげんよう。新天地ですわ、暴れさせていただきますの</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6489,14 +6489,14 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お仲間入りですわね。よろしくですの</t>
+          <t xml:space="preserve">ここなら好きにやれそうですわね。楽しみですの</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6521,14 +6521,14 @@
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">巡り巡って、良い場所にご縁がありましたこと</t>
+          <t xml:space="preserve">まあ、今日から仲間ですわね。よろしくお願いしますの</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6538,12 +6538,12 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6553,14 +6553,14 @@
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ごきげんよう。新天地ですわ、暴れさせていただきますの</t>
+          <t xml:space="preserve">皆様、楽しくやりましょうね</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6585,14 +6585,14 @@
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここなら好きにやれそうですわね。楽しみですの</t>
+          <t xml:space="preserve">あらあら…少し休みますわね</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">draftInterest.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6617,14 +6617,14 @@
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、今日から仲間ですわね。よろしくお願いしますの</t>
+          <t xml:space="preserve">うふふ、ご一緒に楽しくやりましょうよ</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">draftInterest.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6649,14 +6649,14 @@
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">皆様、楽しくやりましょうね</t>
+          <t xml:space="preserve">退屈なプロレスはしないと約束いたしますわ</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6671,7 +6671,7 @@
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">draftJoin.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6681,14 +6681,14 @@
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらあら…少し休みますわね</t>
+          <t xml:space="preserve">ふふ、よろしくお願いしますわぁ</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">draftJoin.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6713,14 +6713,14 @@
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、こういうこともありますわね。ごきげんよう</t>
+          <t xml:space="preserve">お仲間入りですわね。よろしくですの</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6735,7 +6735,7 @@
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">faGreeting.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6745,14 +6745,14 @@
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お邪魔いたしますわ。短い間ですけれど、暴れさせていただきますの</t>
+          <t xml:space="preserve">巡り巡って、良い場所にご縁がありましたこと</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">faSigning.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6777,14 +6777,14 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一時のご縁ですもの、思い切りやらせていただきますわ</t>
+          <t xml:space="preserve">ごきげんよう。新天地ですわ、暴れさせていただきますの</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6799,7 +6799,7 @@
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">faSigning.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6809,14 +6809,14 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うふふ♪見出されるって、とても気分がよいことですね</t>
+          <t xml:space="preserve">ここなら好きにやれそうですわね。楽しみですの</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">faWelcome.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6841,14 +6841,14 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は負けてしまいましたけれど…次はもっとよい試合をしますわ</t>
+          <t xml:space="preserve">まあ、今日から仲間ですわね。よろしくお願いしますの</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6863,7 +6863,7 @@
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">faWelcome.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6873,14 +6873,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいですけれど、俯いていては応援してくださる方に失礼ですもの</t>
+          <t xml:space="preserve">皆様、楽しくやりましょうね</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6895,7 +6895,7 @@
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">injury.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6905,14 +6905,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンはわたくしですの。また守り切りましたわ</t>
+          <t xml:space="preserve">あらあら…少し休みますわね</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">release.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -6937,14 +6937,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よい試合でしたわ。またいつでも挑んでらして</t>
+          <t xml:space="preserve">ふふ、こういうこともありますわね。ごきげんよう</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6959,7 +6959,7 @@
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">rentalGreeting.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -6969,14 +6969,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けてしまいましたわ…でも応援してくださる方がいる限り、立ち上がりますの</t>
+          <t xml:space="preserve">お邪魔いたしますわ。短い間ですけれど、暴れさせていただきますの</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">rentalGreeting.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7001,14 +7001,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ベルトのないわたくしなんて想像もできませんでしたわ。でも、わたくしはわたくしですもの</t>
+          <t xml:space="preserve">一時のご縁ですもの、思い切りやらせていただきますわ</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">scoutGreeting.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7033,14 +7033,14 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">新チャンピオン誕生ですわ。ここからもっと盛り上げますの</t>
+          <t xml:space="preserve">うふふ♪見出されるって、とても気分がよいことですね</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7055,7 +7055,7 @@
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">titleChallengeLoss.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7065,14 +7065,14 @@
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルト、獲ってしまいましたわ。最高の気分ですの</t>
+          <t xml:space="preserve">今日は負けてしまいましたけれど…次はもっとよい試合をしますわ</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7097,14 +7097,14 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、こういうこともありますわね。ごきげんよう</t>
+          <t xml:space="preserve">悔しいですけれど、俯いていては応援してくださる方に失礼ですもの</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7114,12 +7114,12 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[1]</t>
+          <t xml:space="preserve">titleDefense.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7129,14 +7129,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お邪魔いたしますわ。短い間ですけれど、暴れさせていただきますの</t>
+          <t xml:space="preserve">チャンピオンはわたくしですの。また守り切りましたわ</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[2]</t>
+          <t xml:space="preserve">titleDefense.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7161,14 +7161,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一時のご縁ですもの、思い切りやらせていただきますわ</t>
+          <t xml:space="preserve">よい試合でしたわ。またいつでも挑んでらして</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[1]</t>
+          <t xml:space="preserve">titleLoss.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7193,14 +7193,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は負けてしまいましたけれど…次はもっとよい試合をしますわ</t>
+          <t xml:space="preserve">負けてしまいましたわ…でも応援してくださる方がいる限り、立ち上がりますの</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[2]</t>
+          <t xml:space="preserve">titleLoss.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7225,14 +7225,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいですけれど、俯いていては応援してくださる方に失礼ですもの</t>
+          <t xml:space="preserve">…ベルトのないわたくしなんて想像もできませんでしたわ。でも、わたくしはわたくしですもの</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7242,12 +7242,12 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[1]</t>
+          <t xml:space="preserve">titleWin.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7257,14 +7257,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンはわたくしですの。また守り切りましたわ</t>
+          <t xml:space="preserve">新チャンピオン誕生ですわ。ここからもっと盛り上げますの</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7274,12 +7274,12 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[2]</t>
+          <t xml:space="preserve">titleWin.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7289,14 +7289,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よい試合でしたわ。またいつでも挑んでらして</t>
+          <t xml:space="preserve">ベルト、獲ってしまいましたわ。最高の気分ですの</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7306,7 +7306,7 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
@@ -7321,14 +7321,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けてしまいましたわ…でも応援してくださる方がいる限り、立ち上がりますの</t>
+          <t xml:space="preserve">ふふ、こういうこともありますわね。ごきげんよう</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7338,12 +7338,12 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[2]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7353,14 +7353,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ベルトのないわたくしなんて想像もできませんでしたわ。でも、わたくしはわたくしですもの</t>
+          <t xml:space="preserve">お邪魔いたしますわ。短い間ですけれど、暴れさせていただきますの</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7370,12 +7370,12 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[1]</t>
+          <t xml:space="preserve">ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7385,14 +7385,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">新チャンピオン誕生ですわ。ここからもっと盛り上げますの</t>
+          <t xml:space="preserve">一時のご縁ですもの、思い切りやらせていただきますわ</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[2]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7417,14 +7417,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルト、獲ってしまいましたわ。最高の気分ですの</t>
+          <t xml:space="preserve">今日は負けてしまいましたけれど…次はもっとよい試合をしますわ</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7434,29 +7434,29 @@
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">う〜ん…少々、合いませんかしら…</t>
+          <t xml:space="preserve">悔しいですけれど、俯いていては応援してくださる方に失礼ですもの</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7466,29 +7466,29 @@
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、近ごろ少し素っ気ないような</t>
+          <t xml:space="preserve">チャンピオンはわたくしですの。また守り切りましたわ</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7498,29 +7498,29 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">はて…空気が微かに変わりましたかしら</t>
+          <t xml:space="preserve">よい試合でしたわ。またいつでも挑んでらして</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7530,29 +7530,29 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しくお過ごしできますの〜</t>
+          <t xml:space="preserve">負けてしまいましたわ…でも応援してくださる方がいる限り、立ち上がりますの</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7562,29 +7562,29 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の相方。ずっとこのままでいたいものです</t>
+          <t xml:space="preserve">…ベルトのないわたくしなんて想像もできませんでしたわ。でも、わたくしはわたくしですもの</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7594,29 +7594,29 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒にいると、何もかも上手く回る気がして</t>
+          <t xml:space="preserve">新チャンピオン誕生ですわ。ここからもっと盛り上げますの</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7626,29 +7626,29 @@
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">熱い間柄も一区切り。少し寂しいものです</t>
+          <t xml:space="preserve">ベルト、獲ってしまいましたわ。最高の気分ですの</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7663,7 +7663,7 @@
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">bond_39_down.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7673,14 +7673,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ、因縁とて永遠ではありませんもの〜</t>
+          <t xml:space="preserve">う〜ん…少々、合いませんかしら…</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7695,7 +7695,7 @@
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">bond_59_down.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7705,14 +7705,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">良い勝負になりそうです〜。少し燃えてきました</t>
+          <t xml:space="preserve">あら、近ごろ少し素っ気ないような</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">bond_59_down.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7737,14 +7737,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うふふ、負けたくありませんね</t>
+          <t xml:space="preserve">はて…空気が微かに変わりましたかしら</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7759,7 +7759,7 @@
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">bond_60_up.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7769,14 +7769,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">本気でやり合いたい相手など、そういません</t>
+          <t xml:space="preserve">楽しくお過ごしできますの〜</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7791,7 +7791,7 @@
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">bond_80_up.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7801,14 +7801,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うふふ、思い浮かべるだけで力が入ります</t>
+          <t xml:space="preserve">最高の相方。ずっとこのままでいたいものです</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7823,7 +7823,7 @@
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">bond_80_up.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7833,14 +7833,14 @@
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この試合が一番楽しい。ずっとこのままであればよいのに</t>
+          <t xml:space="preserve">一緒にいると、何もかも上手く回る気がして</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7855,7 +7855,7 @@
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">rivalry_29_down.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -7865,14 +7865,14 @@
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">運命の好敵手…そう呼びたくなります</t>
+          <t xml:space="preserve">熱い間柄も一区切り。少し寂しいものです</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">rivalry_29_down.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7897,14 +7897,14 @@
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここは素晴らしい〜。皆さんとやるのが楽しくて</t>
+          <t xml:space="preserve">まぁ、因縁とて永遠ではありませんもの〜</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7919,7 +7919,7 @@
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">rivalry_30_up.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7929,14 +7929,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体、とても居心地がよいのです〜</t>
+          <t xml:space="preserve">良い勝負になりそうです〜。少し燃えてきました</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">rivalry_30_up.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -7961,14 +7961,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">さすがにこれは…笑えません</t>
+          <t xml:space="preserve">うふふ、負けたくありませんね</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -7983,7 +7983,7 @@
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">rivalry_50_up.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -7993,14 +7993,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うふふ…と笑っている場合ではありませんね、これは</t>
+          <t xml:space="preserve">本気でやり合いたい相手など、そういません</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8015,7 +8015,7 @@
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.easygoing.ojousama[1]</t>
+          <t xml:space="preserve">rivalry_50_up.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8025,14 +8025,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">う〜ん…近ごろ少し胸がすっきりしません…</t>
+          <t xml:space="preserve">うふふ、思い浮かべるだけで力が入ります</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8047,7 +8047,7 @@
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.easygoing.ojousama[2]</t>
+          <t xml:space="preserve">rivalry_70_up.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8057,14 +8057,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ大丈夫…ですよね？ 少し不安ですけれど</t>
+          <t xml:space="preserve">この試合が一番楽しい。ずっとこのままであればよいのに</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[1]</t>
+          <t xml:space="preserve">rivalry_70_up.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8089,14 +8089,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">連勝が止まりましたわ…でもまた頑張りますの</t>
+          <t xml:space="preserve">運命の好敵手…そう呼びたくなります</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8106,29 +8106,29 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">trust_above_75.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">傷だらけですけれど、最後まで来てしまいましたわ。ふふ、やるしかありませんわね</t>
+          <t xml:space="preserve">ここは素晴らしい〜。皆さんとやるのが楽しくて</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8138,29 +8138,29 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">trust_above_75.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">さすがに身体が重いですの。でも、締めくくりは楽しませていただきますわ</t>
+          <t xml:space="preserve">この団体、とても居心地がよいのです〜</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8170,29 +8170,29 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">trust_below_20.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、お相手はどなた？ 次から次へと、賑やかですこと</t>
+          <t xml:space="preserve">さすがにこれは…笑えません</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8202,29 +8202,29 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">trust_below_20.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">賑やかな一日になりそうですわね。…面白いですわ</t>
+          <t xml:space="preserve">うふふ…と笑っている場合ではありませんね、これは</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8234,29 +8234,29 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">trust_below_35.easygoing.ojousama[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、お見送りしましたわ。…ふぅ、まだ立っていますのよ。次はどなた？</t>
+          <t xml:space="preserve">う〜ん…近ごろ少し胸がすっきりしません…</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8266,29 +8266,29 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">trust_below_35.easygoing.ojousama[2]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、まだ終わりませんの？ いいですわ、次の方、いらして</t>
+          <t xml:space="preserve">まぁ大丈夫…ですよね？ 少し不安ですけれど</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8298,29 +8298,29 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">素敵な三人でしたわ。この勝利は、お二人と分かち合いたいですの</t>
+          <t xml:space="preserve">連勝が止まりましたわ…でもまた頑張りますの</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8330,12 +8330,12 @@
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">preFinal.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8345,14 +8345,14 @@
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お二人がいてくださったから、安心して戦えましたわ。ふふ</t>
+          <t xml:space="preserve">傷だらけですけれど、最後まで来てしまいましたわ。ふふ、やるしかありませんわね</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8362,12 +8362,12 @@
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">preFinal.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8377,14 +8377,14 @@
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お賞はありがたいですわ。でも……お一人で笑うのは、趣味じゃありませんの</t>
+          <t xml:space="preserve">さすがに身体が重いですの。でも、締めくくりは楽しませていただきますわ</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8394,12 +8394,12 @@
       </c>
       <c r="C254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">preMatch.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8409,14 +8409,14 @@
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次はお三人で勝って、優雅に乾杯したいですわね</t>
+          <t xml:space="preserve">あら、お相手はどなた？ 次から次へと、賑やかですこと</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="C255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">preMatch.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8441,14 +8441,14 @@
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次から次へと来るのですもの。退屈しませんでしたわ。身体は少し重いですけれど</t>
+          <t xml:space="preserve">賑やかな一日になりそうですわね。…面白いですわ</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">survivor.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8473,14 +8473,14 @@
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人お相手したのかしら。まあ、全員お見送りしましたし、よろしいですわね</t>
+          <t xml:space="preserve">一人、お見送りしましたわ。…ふぅ、まだ立っていますのよ。次はどなた？</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8490,12 +8490,12 @@
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">survivor.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8505,14 +8505,14 @@
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらあら、優勝ですって。うまくいくものですわね</t>
+          <t xml:space="preserve">あら、まだ終わりませんの？ いいですわ、次の方、いらして</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8522,12 +8522,12 @@
       </c>
       <c r="C258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">champion.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8537,14 +8537,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やりましたわ〜！ ご褒美が楽しみですわね</t>
+          <t xml:space="preserve">素敵な三人でしたわ。この勝利は、お二人と分かち合いたいですの</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="C259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">champion.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8569,14 +8569,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やりましたわ。この調子で行きますわよ</t>
+          <t xml:space="preserve">お二人がいてくださったから、安心して戦えましたわ。ふふ</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8586,12 +8586,12 @@
       </c>
       <c r="C260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">defiant.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8601,14 +8601,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだまだ楽しめそうですわね</t>
+          <t xml:space="preserve">お賞はありがたいですわ。でも……お一人で笑うのは、趣味じゃありませんの</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8618,12 +8618,12 @@
       </c>
       <c r="C261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">defiant.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8633,14 +8633,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、決勝まで来ちゃいましたわ。楽しみですわね</t>
+          <t xml:space="preserve">次はお三人で勝って、優雅に乾杯したいですわね</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8650,12 +8650,12 @@
       </c>
       <c r="C262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">gauntlet.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8665,14 +8665,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最後の一戦！ 思いっきりやりますわよ</t>
+          <t xml:space="preserve">次から次へと来るのですもの。退屈しませんでしたわ。身体は少し重いですけれど</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8682,12 +8682,12 @@
       </c>
       <c r="C263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">gauntlet.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8697,14 +8697,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">さあ、楽しい時間の始まりですわ</t>
+          <t xml:space="preserve">何人お相手したのかしら。まあ、全員お見送りしましたし、よろしいですわね</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8719,7 +8719,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">champion.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8729,14 +8729,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">気楽に参りましょう。でも負けませんわよ</t>
+          <t xml:space="preserve">あらあら、優勝ですって。うまくいくものですわね</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8751,7 +8751,7 @@
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">champion.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8761,14 +8761,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、わたくしも呼ばれましたの？ 面白そうですわね</t>
+          <t xml:space="preserve">やりましたわ〜！ ご褒美が楽しみですわね</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8783,7 +8783,7 @@
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">postMatchWin.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8793,14 +8793,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらあら、お声がかかってしまって。断る理由もありませんわね</t>
+          <t xml:space="preserve">やりましたわ。この調子で行きますわよ</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="C267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[1]</t>
+          <t xml:space="preserve">postMatchWin.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8825,14 +8825,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力で参りますわ！ よろしくお願いいたしますの</t>
+          <t xml:space="preserve">まだまだ楽しめそうですわね</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[1]</t>
+          <t xml:space="preserve">preFinal.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -8857,14 +8857,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、勝っちゃいましたわ！最高の舞台で、最高の気分ですの！</t>
+          <t xml:space="preserve">あら、決勝まで来ちゃいましたわ。楽しみですわね</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8874,12 +8874,12 @@
       </c>
       <c r="C269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[1]</t>
+          <t xml:space="preserve">preFinal.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -8889,14 +8889,14 @@
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら〜、面白そうな団体ですわね。遊ばせていただきますわ</t>
+          <t xml:space="preserve">最後の一戦！ 思いっきりやりますわよ</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8906,12 +8906,12 @@
       </c>
       <c r="C270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[2]</t>
+          <t xml:space="preserve">preMatch.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -8921,14 +8921,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたくしたちと勝負しません？ きっと楽しいですわよ</t>
+          <t xml:space="preserve">さあ、楽しい時間の始まりですわ</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="C271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[1]</t>
+          <t xml:space="preserve">preMatch.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -8953,14 +8953,14 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら〜、お断りですの？ もったいないですわ</t>
+          <t xml:space="preserve">気楽に参りましょう。でも負けませんわよ</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[2]</t>
+          <t xml:space="preserve">summon.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -8985,14 +8985,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、いいですわ。またの機会にいたしましょう</t>
+          <t xml:space="preserve">あら、わたくしも呼ばれましたの？ 面白そうですわね</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9002,12 +9002,12 @@
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">summon.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9017,14 +9017,14 @@
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらあら、負けてしまいましたわ。でもくよくよしませんわ</t>
+          <t xml:space="preserve">あらあら、お声がかかってしまって。断る理由もありませんわね</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9034,12 +9034,12 @@
       </c>
       <c r="C274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9049,14 +9049,14 @@
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次はもっと上手くやりますわよ〜</t>
+          <t xml:space="preserve">全力で参りますわ！ よろしくお願いいたしますの</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="C275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9081,14 +9081,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらあら、勝ってしまいましたわね</t>
+          <t xml:space="preserve">まあ、勝っちゃいましたわ！最高の舞台で、最高の気分ですの！</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9098,12 +9098,12 @@
       </c>
       <c r="C276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9113,14 +9113,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しい対抗戦でしたわ。またぜひ</t>
+          <t xml:space="preserve">あら〜、面白そうな団体ですわね。遊ばせていただきますわ</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9130,12 +9130,12 @@
       </c>
       <c r="C277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[1]</t>
+          <t xml:space="preserve">ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9145,14 +9145,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、勝ってしまいましたわ〜。うちの団体、なかなかやりますでしょ？</t>
+          <t xml:space="preserve">わたくしたちと勝負しません？ きっと楽しいですわよ</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.easygoing[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[2]</t>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9177,14 +9177,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらあら、勝っちゃいましたわね〜</t>
+          <t xml:space="preserve">あら〜、お断りですの？ もったいないですわ</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.easygoing[3]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[3]</t>
+          <t xml:space="preserve">ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9209,14 +9209,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しかったですわ〜。またやりましょうね</t>
+          <t xml:space="preserve">ま、いいですわ。またの機会にいたしましょう</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9226,29 +9226,29 @@
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">result_lose.ojousama.easygoing[1]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最後まで楽しゅうございましたわ。ありがとうございます</t>
+          <t xml:space="preserve">あらあら、負けてしまいましたわ。でもくよくよしませんわ</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.ojousama.easygoing[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9258,59 +9258,283 @@
       </c>
       <c r="C281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ojousama.easygoing[1]</t>
+          <t xml:space="preserve">result_lose.ojousama.easygoing[2]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">巡り巡って、良い場所にご縁がありましたこと</t>
+          <t xml:space="preserve">次はもっと上手くやりますわよ〜</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あらあら、勝ってしまいましたわね</t>
+        </is>
+      </c>
+    </row>
+    <row r="283" ht="40" customHeight="1">
+      <c r="A283" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.ojousama.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.ojousama.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">楽しい対抗戦でしたわ。またぜひ</t>
+        </is>
+      </c>
+    </row>
+    <row r="284" ht="40" customHeight="1">
+      <c r="A284" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あら、勝ってしまいましたわ〜。うちの団体、なかなかやりますでしょ？</t>
+        </is>
+      </c>
+    </row>
+    <row r="285" ht="40" customHeight="1">
+      <c r="A285" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">ojousama.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あらあら、勝っちゃいましたわね〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="286" ht="40" customHeight="1">
+      <c r="A286" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.ojousama.easygoing[3]</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">ojousama.easygoing[3]</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">楽しかったですわ〜。またやりましょうね</t>
+        </is>
+      </c>
+    </row>
+    <row r="287" ht="40" customHeight="1">
+      <c r="A287" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">最後まで楽しゅうございましたわ。ありがとうございます</t>
+        </is>
+      </c>
+    </row>
+    <row r="288" ht="40" customHeight="1">
+      <c r="A288" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">ojousama.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">巡り巡って、良い場所にご縁がありましたこと</t>
+        </is>
+      </c>
+    </row>
+    <row r="289" ht="40" customHeight="1">
+      <c r="A289" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.ojousama.easygoing[1]</t>
         </is>
       </c>
-      <c r="B282" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C282" t="inlineStr" s="2">
+      <c r="B289" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr" s="12">
+      <c r="D289" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">ojousama.easygoing[1]</t>
         </is>
       </c>
-      <c r="E282" t="inlineStr" s="2">
+      <c r="E289" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F282" t="inlineStr" s="3">
+      <c r="F289" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">うふふ♪見出されるって、とても気分がよいことですね</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H282"/>
+  <autoFilter ref="A1:H289"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/お嬢様×お気楽.xlsx
+++ b/セリフ編集/キャラタイプ別/お嬢様×お気楽.xlsx
@@ -2361,7 +2361,7 @@
       </c>
       <c r="F65" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、わたくし、あの方とやってみたいのです。</t>
+          <t xml:space="preserve">社長、わたくしたち三人で、あちらへ行ってみたいのです。</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2393,7 @@
       </c>
       <c r="F66" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ねえ社長、あの方と当ててくださいません？</t>
+          <t xml:space="preserve">ねえ社長、三人であの団体に当ててくださいません？</t>
         </is>
       </c>
     </row>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="F67" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">思いつきではないのです。あの方と、試合を。</t>
+          <t xml:space="preserve">思いつきではないのです。三人で、あちらへ挑戦を。</t>
         </is>
       </c>
     </row>
